--- a/Mng/Acronyms.xlsx
+++ b/Mng/Acronyms.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DED5B42-7A3A-410C-B70E-9E5ACC532370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9D7C76-1884-481B-92AE-FB6B6187BD0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Acronyms" sheetId="1" r:id="rId1"/>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="850">
   <si>
     <t>GW</t>
   </si>
@@ -2852,6 +2852,12 @@
   </si>
   <si>
     <t>Ct</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>Separator</t>
   </si>
 </sst>
 </file>
@@ -3387,6 +3393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:F994"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9796,17 +9803,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B417" s="5"/>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A417" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="B417" s="5" t="s">
+        <v>849</v>
+      </c>
       <c r="C417" s="5" t="s">
-        <v>156</v>
+        <v>441</v>
       </c>
       <c r="E417" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
-    <row r="418" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B418" s="5"/>
       <c r="C418" s="5" t="s">
         <v>156</v>
@@ -9816,7 +9828,7 @@
         <v/>
       </c>
     </row>
-    <row r="419" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B419" s="5"/>
       <c r="C419" s="5" t="s">
         <v>156</v>
@@ -9826,7 +9838,7 @@
         <v/>
       </c>
     </row>
-    <row r="420" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B420" s="5"/>
       <c r="C420" s="5" t="s">
         <v>156</v>
@@ -9836,7 +9848,7 @@
         <v/>
       </c>
     </row>
-    <row r="421" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B421" s="5"/>
       <c r="C421" s="5" t="s">
         <v>156</v>
@@ -9846,7 +9858,7 @@
         <v/>
       </c>
     </row>
-    <row r="422" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B422" s="5"/>
       <c r="C422" s="5" t="s">
         <v>156</v>
@@ -9856,7 +9868,7 @@
         <v/>
       </c>
     </row>
-    <row r="423" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B423" s="5"/>
       <c r="C423" s="5" t="s">
         <v>156</v>
@@ -9866,7 +9878,7 @@
         <v/>
       </c>
     </row>
-    <row r="424" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B424" s="5"/>
       <c r="C424" s="5" t="s">
         <v>156</v>
@@ -9876,7 +9888,7 @@
         <v/>
       </c>
     </row>
-    <row r="425" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B425" s="5"/>
       <c r="C425" s="5" t="s">
         <v>156</v>
@@ -9886,7 +9898,7 @@
         <v/>
       </c>
     </row>
-    <row r="426" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B426" s="5"/>
       <c r="C426" s="5" t="s">
         <v>156</v>
@@ -9896,7 +9908,7 @@
         <v/>
       </c>
     </row>
-    <row r="427" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B427" s="5"/>
       <c r="C427" s="5" t="s">
         <v>156</v>
@@ -9906,7 +9918,7 @@
         <v/>
       </c>
     </row>
-    <row r="428" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B428" s="5"/>
       <c r="C428" s="5" t="s">
         <v>156</v>
@@ -9916,7 +9928,7 @@
         <v/>
       </c>
     </row>
-    <row r="429" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B429" s="5"/>
       <c r="C429" s="5" t="s">
         <v>156</v>
@@ -9926,7 +9938,7 @@
         <v/>
       </c>
     </row>
-    <row r="430" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B430" s="5"/>
       <c r="C430" s="5" t="s">
         <v>156</v>
@@ -9936,7 +9948,7 @@
         <v/>
       </c>
     </row>
-    <row r="431" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B431" s="5"/>
       <c r="C431" s="5" t="s">
         <v>156</v>
@@ -9946,7 +9958,7 @@
         <v/>
       </c>
     </row>
-    <row r="432" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B432" s="5"/>
       <c r="C432" s="5" t="s">
         <v>156</v>
@@ -15600,6 +15612,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4B7870-5A97-4356-98C4-DC188A0A60A4}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:A36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>

--- a/Mng/Acronyms.xlsx
+++ b/Mng/Acronyms.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9D7C76-1884-481B-92AE-FB6B6187BD0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8DFF767-AA5C-4033-B498-429BCF972505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Acronyms" sheetId="1" r:id="rId1"/>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="852">
   <si>
     <t>GW</t>
   </si>
@@ -2858,6 +2858,13 @@
   </si>
   <si>
     <t>Separator</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Different context to other M.
+Needed for WS_Mdl python lib, where MdlN is used as an arg, Mdl_N is a class, so M is the instance of this class based on the arg. Using M for this makes it very easy to reference.</t>
   </si>
 </sst>
 </file>
@@ -2955,7 +2962,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2993,6 +3000,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9818,10 +9828,18 @@
         <v/>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B418" s="5"/>
+    <row r="418" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A418" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="B418" s="5" t="s">
+        <v>850</v>
+      </c>
       <c r="C418" s="5" t="s">
-        <v>156</v>
+        <v>423</v>
+      </c>
+      <c r="D418" s="17" t="s">
+        <v>851</v>
       </c>
       <c r="E418" t="str">
         <f t="shared" si="12"/>

--- a/Mng/Acronyms.xlsx
+++ b/Mng/Acronyms.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FECF13-5F4B-4E62-A134-F24849EB22F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D4AB3A-6499-4EF5-A742-D418C8015072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1440" yWindow="5040" windowWidth="15330" windowHeight="7170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Acronyms" sheetId="1" r:id="rId1"/>
@@ -2883,7 +2883,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2938,6 +2938,13 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2974,7 +2981,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3015,6 +3022,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3457,7 +3468,7 @@
         <v>292</v>
       </c>
       <c r="E2" t="str">
-        <f>IF(AND(A2=A1,A2&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E2:E33" si="0">IF(AND(A2=A1,A2&lt;&gt;""),1,"")</f>
         <v/>
       </c>
       <c r="F2" s="4">
@@ -3476,7 +3487,7 @@
         <v>292</v>
       </c>
       <c r="E3" t="str">
-        <f>IF(AND(A3=A2,A3&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3491,7 +3502,7 @@
         <v>423</v>
       </c>
       <c r="E4" t="str">
-        <f>IF(AND(A4=A3,A4&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3506,7 +3517,7 @@
         <v>423</v>
       </c>
       <c r="E5" t="str">
-        <f>IF(AND(A5=A4,A5&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3522,7 +3533,7 @@
       </c>
       <c r="D6" s="5"/>
       <c r="E6" t="str">
-        <f>IF(AND(A6=A5,A6&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3537,7 +3548,7 @@
         <v>300</v>
       </c>
       <c r="E7" t="str">
-        <f>IF(AND(A7=A6,A7&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3552,7 +3563,7 @@
         <v>300</v>
       </c>
       <c r="E8" t="str">
-        <f>IF(AND(A8=A7,A8&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3567,7 +3578,7 @@
         <v>300</v>
       </c>
       <c r="E9" t="str">
-        <f>IF(AND(A9=A8,A9&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3583,7 +3594,7 @@
       </c>
       <c r="D10" s="5"/>
       <c r="E10" t="str">
-        <f>IF(AND(A10=A9,A10&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3601,7 +3612,7 @@
         <v>159</v>
       </c>
       <c r="E11">
-        <f>IF(AND(A11=A10,A11&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3619,23 +3630,22 @@
         <v>155</v>
       </c>
       <c r="E12">
-        <f>IF(AND(A12=A11,A12&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" t="str">
-        <f>IF(AND(A13=A12,A13&lt;&gt;""),1,"")</f>
+      <c r="E13" s="19" t="str">
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3665,7 +3675,7 @@
         <v>290</v>
       </c>
       <c r="E15" t="str">
-        <f>IF(AND(A15=A14,A15&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3680,7 +3690,7 @@
         <v>290</v>
       </c>
       <c r="E16" t="str">
-        <f>IF(AND(A16=A15,A16&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3695,7 +3705,7 @@
         <v>290</v>
       </c>
       <c r="E17" t="str">
-        <f>IF(AND(A17=A16,A17&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3711,7 +3721,7 @@
       </c>
       <c r="D18" s="5"/>
       <c r="E18" t="str">
-        <f>IF(AND(A18=A17,A18&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3726,7 +3736,7 @@
         <v>300</v>
       </c>
       <c r="E19" t="str">
-        <f>IF(AND(A19=A18,A19&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3741,7 +3751,7 @@
         <v>300</v>
       </c>
       <c r="E20" t="str">
-        <f>IF(AND(A20=A19,A20&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3759,7 +3769,7 @@
         <v>836</v>
       </c>
       <c r="E21" t="str">
-        <f>IF(AND(A21=A20,A21&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3775,7 +3785,7 @@
       </c>
       <c r="D22" s="5"/>
       <c r="E22" t="str">
-        <f>IF(AND(A22=A21,A22&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3793,7 +3803,7 @@
         <v>789</v>
       </c>
       <c r="E23" t="str">
-        <f>IF(AND(A23=A22,A23&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3808,7 +3818,7 @@
         <v>300</v>
       </c>
       <c r="E24" t="str">
-        <f>IF(AND(A24=A23,A24&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3824,7 +3834,7 @@
       </c>
       <c r="D25" s="5"/>
       <c r="E25" t="str">
-        <f>IF(AND(A25=A24,A25&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3839,7 +3849,7 @@
         <v>290</v>
       </c>
       <c r="E26" t="str">
-        <f>IF(AND(A26=A25,A26&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3854,7 +3864,7 @@
         <v>292</v>
       </c>
       <c r="E27" t="str">
-        <f>IF(AND(A27=A26,A27&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3870,7 +3880,7 @@
       </c>
       <c r="D28" s="5"/>
       <c r="E28" t="str">
-        <f>IF(AND(A28=A27,A28&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3885,7 +3895,7 @@
         <v>292</v>
       </c>
       <c r="E29">
-        <f>IF(AND(A29=A28,A29&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3900,7 +3910,7 @@
         <v>292</v>
       </c>
       <c r="E30" t="str">
-        <f>IF(AND(A30=A29,A30&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3915,7 +3925,7 @@
         <v>290</v>
       </c>
       <c r="E31" t="str">
-        <f>IF(AND(A31=A30,A31&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3930,7 +3940,7 @@
         <v>292</v>
       </c>
       <c r="E32" t="str">
-        <f>IF(AND(A32=A31,A32&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3945,7 +3955,7 @@
         <v>300</v>
       </c>
       <c r="E33" t="str">
-        <f>IF(AND(A33=A32,A33&lt;&gt;""),1,"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -3961,7 +3971,7 @@
       </c>
       <c r="D34" s="5"/>
       <c r="E34" t="str">
-        <f>IF(AND(A34=A33,A34&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E34:E65" si="1">IF(AND(A34=A33,A34&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -3976,7 +3986,7 @@
         <v>423</v>
       </c>
       <c r="E35" t="str">
-        <f>IF(AND(A35=A34,A35&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3991,7 +4001,7 @@
         <v>300</v>
       </c>
       <c r="E36" t="str">
-        <f>IF(AND(A36=A35,A36&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4006,7 +4016,7 @@
         <v>593</v>
       </c>
       <c r="E37" t="str">
-        <f>IF(AND(A37=A36,A37&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4021,7 +4031,7 @@
         <v>300</v>
       </c>
       <c r="E38" t="str">
-        <f>IF(AND(A38=A37,A38&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4036,7 +4046,7 @@
         <v>300</v>
       </c>
       <c r="E39" t="str">
-        <f>IF(AND(A39=A38,A39&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4052,7 +4062,7 @@
       </c>
       <c r="D40" s="5"/>
       <c r="E40" t="str">
-        <f>IF(AND(A40=A39,A40&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4067,7 +4077,7 @@
         <v>292</v>
       </c>
       <c r="E41" t="str">
-        <f>IF(AND(A41=A40,A41&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4082,7 +4092,7 @@
         <v>300</v>
       </c>
       <c r="E42" t="str">
-        <f>IF(AND(A42=A41,A42&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4097,7 +4107,7 @@
         <v>292</v>
       </c>
       <c r="E43" t="str">
-        <f>IF(AND(A43=A42,A43&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4112,7 +4122,7 @@
         <v>300</v>
       </c>
       <c r="E44" t="str">
-        <f>IF(AND(A44=A43,A44&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4127,7 +4137,7 @@
         <v>292</v>
       </c>
       <c r="E45" t="str">
-        <f>IF(AND(A45=A44,A45&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4142,7 +4152,7 @@
         <v>300</v>
       </c>
       <c r="E46" t="str">
-        <f>IF(AND(A46=A45,A46&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4157,7 +4167,7 @@
         <v>300</v>
       </c>
       <c r="E47" t="str">
-        <f>IF(AND(A47=A46,A47&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4172,7 +4182,7 @@
         <v>300</v>
       </c>
       <c r="E48" t="str">
-        <f>IF(AND(A48=A47,A48&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4187,7 +4197,7 @@
         <v>300</v>
       </c>
       <c r="E49" t="str">
-        <f>IF(AND(A49=A48,A49&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4202,7 +4212,7 @@
         <v>292</v>
       </c>
       <c r="E50" t="str">
-        <f>IF(AND(A50=A49,A50&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4217,7 +4227,7 @@
         <v>423</v>
       </c>
       <c r="E51" t="str">
-        <f>IF(AND(A51=A50,A51&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4232,7 +4242,7 @@
         <v>292</v>
       </c>
       <c r="E52" t="str">
-        <f>IF(AND(A52=A51,A52&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4248,7 +4258,7 @@
       </c>
       <c r="D53" s="5"/>
       <c r="E53" t="str">
-        <f>IF(AND(A53=A52,A53&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4263,7 +4273,7 @@
         <v>423</v>
       </c>
       <c r="E54">
-        <f>IF(AND(A54=A53,A54&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4278,7 +4288,7 @@
         <v>293</v>
       </c>
       <c r="E55">
-        <f>IF(AND(A55=A54,A55&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4293,7 +4303,7 @@
         <v>300</v>
       </c>
       <c r="E56">
-        <f>IF(AND(A56=A55,A56&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4308,7 +4318,7 @@
         <v>292</v>
       </c>
       <c r="E57" t="str">
-        <f>IF(AND(A57=A56,A57&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4326,7 +4336,7 @@
         <v>159</v>
       </c>
       <c r="E58">
-        <f>IF(AND(A58=A57,A58&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4341,7 +4351,7 @@
         <v>423</v>
       </c>
       <c r="E59">
-        <f>IF(AND(A59=A58,A59&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -4356,7 +4366,7 @@
         <v>292</v>
       </c>
       <c r="E60" t="str">
-        <f>IF(AND(A60=A59,A60&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4368,7 +4378,7 @@
         <v>855</v>
       </c>
       <c r="E61" t="str">
-        <f>IF(AND(A61=A60,A61&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4383,7 +4393,7 @@
         <v>300</v>
       </c>
       <c r="E62" t="str">
-        <f>IF(AND(A62=A61,A62&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4398,7 +4408,7 @@
         <v>292</v>
       </c>
       <c r="E63" t="str">
-        <f>IF(AND(A63=A62,A63&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4413,7 +4423,7 @@
         <v>423</v>
       </c>
       <c r="E64" t="str">
-        <f>IF(AND(A64=A63,A64&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4428,7 +4438,7 @@
         <v>182</v>
       </c>
       <c r="E65" t="str">
-        <f>IF(AND(A65=A64,A65&lt;&gt;""),1,"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -4444,7 +4454,7 @@
       </c>
       <c r="D66" s="5"/>
       <c r="E66" t="str">
-        <f>IF(AND(A66=A65,A66&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E66:E97" si="2">IF(AND(A66=A65,A66&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -4459,7 +4469,7 @@
         <v>300</v>
       </c>
       <c r="E67" t="str">
-        <f>IF(AND(A67=A66,A67&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4474,7 +4484,7 @@
         <v>292</v>
       </c>
       <c r="E68" t="str">
-        <f>IF(AND(A68=A67,A68&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4489,7 +4499,7 @@
         <v>441</v>
       </c>
       <c r="E69" t="str">
-        <f>IF(AND(A69=A68,A69&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4504,7 +4514,7 @@
         <v>290</v>
       </c>
       <c r="E70" t="str">
-        <f>IF(AND(A70=A69,A70&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4519,7 +4529,7 @@
         <v>593</v>
       </c>
       <c r="E71">
-        <f>IF(AND(A71=A70,A71&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4534,7 +4544,7 @@
         <v>300</v>
       </c>
       <c r="E72" t="str">
-        <f>IF(AND(A72=A71,A72&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4549,7 +4559,7 @@
         <v>593</v>
       </c>
       <c r="E73" t="str">
-        <f>IF(AND(A73=A72,A73&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4564,7 +4574,7 @@
         <v>593</v>
       </c>
       <c r="E74" t="str">
-        <f>IF(AND(A74=A73,A74&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4579,7 +4589,7 @@
         <v>300</v>
       </c>
       <c r="E75" t="str">
-        <f>IF(AND(A75=A74,A75&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4594,7 +4604,7 @@
         <v>292</v>
       </c>
       <c r="E76" t="str">
-        <f>IF(AND(A76=A75,A76&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4609,7 +4619,7 @@
         <v>290</v>
       </c>
       <c r="E77" t="str">
-        <f>IF(AND(A77=A76,A77&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4624,7 +4634,7 @@
         <v>290</v>
       </c>
       <c r="E78" t="str">
-        <f>IF(AND(A78=A77,A78&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4639,7 +4649,7 @@
         <v>290</v>
       </c>
       <c r="E79" t="str">
-        <f>IF(AND(A79=A78,A79&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4654,7 +4664,7 @@
         <v>593</v>
       </c>
       <c r="E80">
-        <f>IF(AND(A80=A79,A80&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4669,7 +4679,7 @@
         <v>292</v>
       </c>
       <c r="E81" t="str">
-        <f>IF(AND(A81=A80,A81&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4684,7 +4694,7 @@
         <v>292</v>
       </c>
       <c r="E82" t="str">
-        <f>IF(AND(A82=A81,A82&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4699,7 +4709,7 @@
         <v>292</v>
       </c>
       <c r="E83" t="str">
-        <f>IF(AND(A83=A82,A83&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4714,7 +4724,7 @@
         <v>300</v>
       </c>
       <c r="E84" t="str">
-        <f>IF(AND(A84=A83,A84&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4730,7 +4740,7 @@
       </c>
       <c r="D85" s="5"/>
       <c r="E85" t="str">
-        <f>IF(AND(A85=A84,A85&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4746,7 +4756,7 @@
       </c>
       <c r="D86" s="5"/>
       <c r="E86" t="str">
-        <f>IF(AND(A86=A85,A86&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4762,7 +4772,7 @@
       </c>
       <c r="D87" s="5"/>
       <c r="E87" t="str">
-        <f>IF(AND(A87=A86,A87&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4777,7 +4787,7 @@
         <v>290</v>
       </c>
       <c r="E88" t="str">
-        <f>IF(AND(A88=A87,A88&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4793,7 +4803,7 @@
       </c>
       <c r="D89" s="5"/>
       <c r="E89" t="str">
-        <f>IF(AND(A89=A88,A89&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4811,7 +4821,7 @@
         <v>155</v>
       </c>
       <c r="E90">
-        <f>IF(AND(A90=A89,A90&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4826,7 +4836,7 @@
         <v>290</v>
       </c>
       <c r="E91" t="str">
-        <f>IF(AND(A91=A90,A91&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4841,7 +4851,7 @@
         <v>300</v>
       </c>
       <c r="E92" t="str">
-        <f>IF(AND(A92=A91,A92&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4856,7 +4866,7 @@
         <v>300</v>
       </c>
       <c r="E93" t="str">
-        <f>IF(AND(A93=A92,A93&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4871,7 +4881,7 @@
         <v>292</v>
       </c>
       <c r="E94" t="str">
-        <f>IF(AND(A94=A93,A94&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4886,7 +4896,7 @@
         <v>290</v>
       </c>
       <c r="E95" t="str">
-        <f>IF(AND(A95=A94,A95&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4901,7 +4911,7 @@
         <v>290</v>
       </c>
       <c r="E96" t="str">
-        <f>IF(AND(A96=A95,A96&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4916,7 +4926,7 @@
         <v>300</v>
       </c>
       <c r="E97" t="str">
-        <f>IF(AND(A97=A96,A97&lt;&gt;""),1,"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4932,7 +4942,7 @@
       </c>
       <c r="D98" s="5"/>
       <c r="E98" t="str">
-        <f>IF(AND(A98=A97,A98&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E98:E129" si="3">IF(AND(A98=A97,A98&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -4947,7 +4957,7 @@
         <v>300</v>
       </c>
       <c r="E99" t="str">
-        <f>IF(AND(A99=A98,A99&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4962,7 +4972,7 @@
         <v>300</v>
       </c>
       <c r="E100" t="str">
-        <f>IF(AND(A100=A99,A100&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4977,7 +4987,7 @@
         <v>300</v>
       </c>
       <c r="E101" t="str">
-        <f>IF(AND(A101=A100,A101&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4992,7 +5002,7 @@
         <v>300</v>
       </c>
       <c r="E102" t="str">
-        <f>IF(AND(A102=A101,A102&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5007,7 +5017,7 @@
         <v>593</v>
       </c>
       <c r="E103">
-        <f>IF(AND(A103=A102,A103&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5022,7 +5032,7 @@
         <v>300</v>
       </c>
       <c r="E104" t="str">
-        <f>IF(AND(A104=A103,A104&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5037,7 +5047,7 @@
         <v>292</v>
       </c>
       <c r="E105" t="str">
-        <f>IF(AND(A105=A104,A105&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5052,7 +5062,7 @@
         <v>300</v>
       </c>
       <c r="E106" t="str">
-        <f>IF(AND(A106=A105,A106&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5067,7 +5077,7 @@
         <v>300</v>
       </c>
       <c r="E107" t="str">
-        <f>IF(AND(A107=A106,A107&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5083,7 +5093,7 @@
       </c>
       <c r="D108" s="5"/>
       <c r="E108" t="str">
-        <f>IF(AND(A108=A107,A108&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5098,7 +5108,7 @@
         <v>292</v>
       </c>
       <c r="E109">
-        <f>IF(AND(A109=A108,A109&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5113,7 +5123,7 @@
         <v>292</v>
       </c>
       <c r="E110" t="str">
-        <f>IF(AND(A110=A109,A110&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5128,7 +5138,7 @@
         <v>292</v>
       </c>
       <c r="E111" t="str">
-        <f>IF(AND(A111=A110,A111&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5143,7 +5153,7 @@
         <v>290</v>
       </c>
       <c r="E112" t="str">
-        <f>IF(AND(A112=A111,A112&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5158,7 +5168,7 @@
         <v>300</v>
       </c>
       <c r="E113" t="str">
-        <f>IF(AND(A113=A112,A113&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5173,7 +5183,7 @@
         <v>290</v>
       </c>
       <c r="E114" t="str">
-        <f>IF(AND(A114=A113,A114&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5188,7 +5198,7 @@
         <v>300</v>
       </c>
       <c r="E115" t="str">
-        <f>IF(AND(A115=A114,A115&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5203,7 +5213,7 @@
         <v>300</v>
       </c>
       <c r="E116" t="str">
-        <f>IF(AND(A116=A115,A116&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5218,7 +5228,7 @@
         <v>292</v>
       </c>
       <c r="E117" t="str">
-        <f>IF(AND(A117=A116,A117&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5233,7 +5243,7 @@
         <v>441</v>
       </c>
       <c r="E118" t="str">
-        <f>IF(AND(A118=A117,A118&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5249,7 +5259,7 @@
       </c>
       <c r="D119" s="5"/>
       <c r="E119" t="str">
-        <f>IF(AND(A119=A118,A119&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5264,7 +5274,7 @@
         <v>290</v>
       </c>
       <c r="E120" t="str">
-        <f>IF(AND(A120=A119,A120&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5280,7 +5290,7 @@
       </c>
       <c r="D121" s="5"/>
       <c r="E121" t="str">
-        <f>IF(AND(A121=A120,A121&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5296,7 +5306,7 @@
       </c>
       <c r="D122" s="5"/>
       <c r="E122" t="str">
-        <f>IF(AND(A122=A121,A122&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5311,7 +5321,7 @@
         <v>292</v>
       </c>
       <c r="E123" t="str">
-        <f>IF(AND(A123=A122,A123&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5326,7 +5336,7 @@
         <v>300</v>
       </c>
       <c r="E124" t="str">
-        <f>IF(AND(A124=A123,A124&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5341,7 +5351,7 @@
         <v>292</v>
       </c>
       <c r="E125" t="str">
-        <f>IF(AND(A125=A124,A125&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5356,7 +5366,7 @@
         <v>593</v>
       </c>
       <c r="E126" t="str">
-        <f>IF(AND(A126=A125,A126&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5372,7 +5382,7 @@
       </c>
       <c r="D127" s="5"/>
       <c r="E127" t="str">
-        <f>IF(AND(A127=A126,A127&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5387,7 +5397,7 @@
         <v>290</v>
       </c>
       <c r="E128" t="str">
-        <f>IF(AND(A128=A127,A128&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5403,7 +5413,7 @@
       </c>
       <c r="D129" s="5"/>
       <c r="E129" t="str">
-        <f>IF(AND(A129=A128,A129&lt;&gt;""),1,"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -5421,7 +5431,7 @@
         <v>159</v>
       </c>
       <c r="E130">
-        <f>IF(AND(A130=A129,A130&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E130:E161" si="4">IF(AND(A130=A129,A130&lt;&gt;""),1,"")</f>
         <v>1</v>
       </c>
     </row>
@@ -5436,7 +5446,7 @@
         <v>593</v>
       </c>
       <c r="E131" t="str">
-        <f>IF(AND(A131=A130,A131&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5451,7 +5461,7 @@
         <v>300</v>
       </c>
       <c r="E132" t="str">
-        <f>IF(AND(A132=A131,A132&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5466,7 +5476,7 @@
         <v>300</v>
       </c>
       <c r="E133" t="str">
-        <f>IF(AND(A133=A132,A133&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5481,7 +5491,7 @@
         <v>292</v>
       </c>
       <c r="E134" t="str">
-        <f>IF(AND(A134=A133,A134&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5497,7 +5507,7 @@
       </c>
       <c r="D135" s="5"/>
       <c r="E135" t="str">
-        <f>IF(AND(A135=A134,A135&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5512,7 +5522,7 @@
         <v>293</v>
       </c>
       <c r="E136" t="str">
-        <f>IF(AND(A136=A135,A136&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5528,7 +5538,7 @@
       </c>
       <c r="D137" s="5"/>
       <c r="E137" t="str">
-        <f>IF(AND(A137=A136,A137&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5543,7 +5553,7 @@
         <v>290</v>
       </c>
       <c r="E138" t="str">
-        <f>IF(AND(A138=A137,A138&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5558,7 +5568,7 @@
         <v>290</v>
       </c>
       <c r="E139" t="str">
-        <f>IF(AND(A139=A138,A139&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5573,7 +5583,7 @@
         <v>290</v>
       </c>
       <c r="E140" t="str">
-        <f>IF(AND(A140=A139,A140&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5588,7 +5598,7 @@
         <v>290</v>
       </c>
       <c r="E141" t="str">
-        <f>IF(AND(A141=A140,A141&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5603,7 +5613,7 @@
         <v>292</v>
       </c>
       <c r="E142" t="str">
-        <f>IF(AND(A142=A141,A142&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5618,7 +5628,7 @@
         <v>292</v>
       </c>
       <c r="E143" t="str">
-        <f>IF(AND(A143=A142,A143&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5633,7 +5643,7 @@
         <v>290</v>
       </c>
       <c r="E144" t="str">
-        <f>IF(AND(A144=A143,A144&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5649,7 +5659,7 @@
       </c>
       <c r="D145" s="5"/>
       <c r="E145" t="str">
-        <f>IF(AND(A145=A144,A145&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5664,7 +5674,7 @@
         <v>290</v>
       </c>
       <c r="E146" t="str">
-        <f>IF(AND(A146=A145,A146&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5680,7 +5690,7 @@
       </c>
       <c r="D147" s="5"/>
       <c r="E147" t="str">
-        <f>IF(AND(A147=A146,A147&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5695,7 +5705,7 @@
         <v>290</v>
       </c>
       <c r="E148" t="str">
-        <f>IF(AND(A148=A147,A148&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5710,7 +5720,7 @@
         <v>290</v>
       </c>
       <c r="E149" t="str">
-        <f>IF(AND(A149=A148,A149&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5725,7 +5735,7 @@
         <v>292</v>
       </c>
       <c r="E150" t="str">
-        <f>IF(AND(A150=A149,A150&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5740,7 +5750,7 @@
         <v>290</v>
       </c>
       <c r="E151" t="str">
-        <f>IF(AND(A151=A150,A151&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5755,7 +5765,7 @@
         <v>292</v>
       </c>
       <c r="E152">
-        <f>IF(AND(A152=A151,A152&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5770,7 +5780,7 @@
         <v>292</v>
       </c>
       <c r="E153" t="str">
-        <f>IF(AND(A153=A152,A153&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5785,7 +5795,7 @@
         <v>292</v>
       </c>
       <c r="E154" t="str">
-        <f>IF(AND(A154=A153,A154&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5800,7 +5810,7 @@
         <v>292</v>
       </c>
       <c r="E155" t="str">
-        <f>IF(AND(A155=A154,A155&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5815,7 +5825,7 @@
         <v>300</v>
       </c>
       <c r="E156">
-        <f>IF(AND(A156=A155,A156&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5830,7 +5840,7 @@
         <v>290</v>
       </c>
       <c r="E157" t="str">
-        <f>IF(AND(A157=A156,A157&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5845,7 +5855,7 @@
         <v>292</v>
       </c>
       <c r="E158" t="str">
-        <f>IF(AND(A158=A157,A158&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5860,7 +5870,7 @@
         <v>593</v>
       </c>
       <c r="E159" t="str">
-        <f>IF(AND(A159=A158,A159&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5875,7 +5885,7 @@
         <v>300</v>
       </c>
       <c r="E160" t="str">
-        <f>IF(AND(A160=A159,A160&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5890,7 +5900,7 @@
         <v>300</v>
       </c>
       <c r="E161" t="str">
-        <f>IF(AND(A161=A160,A161&lt;&gt;""),1,"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -5905,7 +5915,7 @@
         <v>300</v>
       </c>
       <c r="E162" t="str">
-        <f>IF(AND(A162=A161,A162&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E162:E173" si="5">IF(AND(A162=A161,A162&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -5920,7 +5930,7 @@
         <v>593</v>
       </c>
       <c r="E163" t="str">
-        <f>IF(AND(A163=A162,A163&lt;&gt;""),1,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5938,7 +5948,7 @@
         <v>709</v>
       </c>
       <c r="E164" t="str">
-        <f>IF(AND(A164=A163,A164&lt;&gt;""),1,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5953,7 +5963,7 @@
         <v>300</v>
       </c>
       <c r="E165" t="str">
-        <f>IF(AND(A165=A164,A165&lt;&gt;""),1,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5965,7 +5975,7 @@
         <v>853</v>
       </c>
       <c r="E166" t="str">
-        <f>IF(AND(A166=A165,A166&lt;&gt;""),1,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5980,7 +5990,7 @@
         <v>290</v>
       </c>
       <c r="E167" t="str">
-        <f>IF(AND(A167=A166,A167&lt;&gt;""),1,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -5995,7 +6005,7 @@
         <v>292</v>
       </c>
       <c r="E168" t="str">
-        <f>IF(AND(A168=A167,A168&lt;&gt;""),1,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6010,7 +6020,7 @@
         <v>300</v>
       </c>
       <c r="E169" t="str">
-        <f>IF(AND(A169=A168,A169&lt;&gt;""),1,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6025,7 +6035,7 @@
         <v>423</v>
       </c>
       <c r="E170" t="str">
-        <f>IF(AND(A170=A169,A170&lt;&gt;""),1,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6040,7 +6050,7 @@
         <v>300</v>
       </c>
       <c r="E171" t="str">
-        <f>IF(AND(A171=A170,A171&lt;&gt;""),1,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6055,7 +6065,7 @@
         <v>300</v>
       </c>
       <c r="E172" t="str">
-        <f>IF(AND(A172=A171,A172&lt;&gt;""),1,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6070,7 +6080,7 @@
         <v>290</v>
       </c>
       <c r="E173" t="str">
-        <f>IF(AND(A173=A172,A173&lt;&gt;""),1,"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6145,7 +6155,7 @@
         <v>302</v>
       </c>
       <c r="E178">
-        <f>IF(AND(A178=A177,A178&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E178:E209" si="6">IF(AND(A178=A177,A178&lt;&gt;""),1,"")</f>
         <v>1</v>
       </c>
     </row>
@@ -6163,7 +6173,7 @@
         <v>302</v>
       </c>
       <c r="E179">
-        <f>IF(AND(A179=A178,A179&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -6181,7 +6191,7 @@
         <v>742</v>
       </c>
       <c r="E180" t="str">
-        <f>IF(AND(A180=A179,A180&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6196,7 +6206,7 @@
         <v>423</v>
       </c>
       <c r="E181">
-        <f>IF(AND(A181=A180,A181&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -6211,7 +6221,7 @@
         <v>292</v>
       </c>
       <c r="E182">
-        <f>IF(AND(A182=A181,A182&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -6226,7 +6236,7 @@
         <v>593</v>
       </c>
       <c r="E183" t="str">
-        <f>IF(AND(A183=A182,A183&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6241,7 +6251,7 @@
         <v>292</v>
       </c>
       <c r="E184" t="str">
-        <f>IF(AND(A184=A183,A184&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6256,7 +6266,7 @@
         <v>300</v>
       </c>
       <c r="E185" t="str">
-        <f>IF(AND(A185=A184,A185&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6271,7 +6281,7 @@
         <v>290</v>
       </c>
       <c r="E186" t="str">
-        <f>IF(AND(A186=A185,A186&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6286,7 +6296,7 @@
         <v>593</v>
       </c>
       <c r="E187" t="str">
-        <f>IF(AND(A187=A186,A187&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6301,7 +6311,7 @@
         <v>301</v>
       </c>
       <c r="E188" t="str">
-        <f>IF(AND(A188=A187,A188&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6319,7 +6329,7 @@
         <v>302</v>
       </c>
       <c r="E189">
-        <f>IF(AND(A189=A188,A189&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -6334,7 +6344,7 @@
         <v>292</v>
       </c>
       <c r="E190" t="str">
-        <f>IF(AND(A190=A189,A190&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6349,7 +6359,7 @@
         <v>290</v>
       </c>
       <c r="E191" t="str">
-        <f>IF(AND(A191=A190,A191&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6364,7 +6374,7 @@
         <v>290</v>
       </c>
       <c r="E192" t="str">
-        <f>IF(AND(A192=A191,A192&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6380,7 +6390,7 @@
       </c>
       <c r="D193" s="5"/>
       <c r="E193" t="str">
-        <f>IF(AND(A193=A192,A193&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6396,7 +6406,7 @@
       </c>
       <c r="D194" s="5"/>
       <c r="E194" t="str">
-        <f>IF(AND(A194=A193,A194&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6414,7 +6424,7 @@
         <v>302</v>
       </c>
       <c r="E195">
-        <f>IF(AND(A195=A194,A195&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -6432,11 +6442,11 @@
         <v>302</v>
       </c>
       <c r="E196">
-        <f>IF(AND(A196=A195,A196&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A197" s="5" t="s">
         <v>280</v>
       </c>
@@ -6450,7 +6460,7 @@
         <v>851</v>
       </c>
       <c r="E197">
-        <f>IF(AND(A197=A196,A197&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -6465,7 +6475,7 @@
         <v>593</v>
       </c>
       <c r="E198" t="str">
-        <f>IF(AND(A198=A197,A198&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6480,7 +6490,7 @@
         <v>182</v>
       </c>
       <c r="E199" t="str">
-        <f>IF(AND(A199=A198,A199&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6495,7 +6505,7 @@
         <v>693</v>
       </c>
       <c r="E200" t="str">
-        <f>IF(AND(A200=A199,A200&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6510,7 +6520,7 @@
         <v>292</v>
       </c>
       <c r="E201" t="str">
-        <f>IF(AND(A201=A200,A201&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6525,7 +6535,7 @@
         <v>292</v>
       </c>
       <c r="E202" t="str">
-        <f>IF(AND(A202=A201,A202&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6540,7 +6550,7 @@
         <v>290</v>
       </c>
       <c r="E203" t="str">
-        <f>IF(AND(A203=A202,A203&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6555,7 +6565,7 @@
         <v>292</v>
       </c>
       <c r="E204" t="str">
-        <f>IF(AND(A204=A203,A204&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6570,7 +6580,7 @@
         <v>292</v>
       </c>
       <c r="E205" t="str">
-        <f>IF(AND(A205=A204,A205&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6585,7 +6595,7 @@
         <v>182</v>
       </c>
       <c r="E206" t="str">
-        <f>IF(AND(A206=A205,A206&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6600,7 +6610,7 @@
         <v>292</v>
       </c>
       <c r="E207" t="str">
-        <f>IF(AND(A207=A206,A207&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6616,7 +6626,7 @@
       </c>
       <c r="D208" s="5"/>
       <c r="E208" t="str">
-        <f>IF(AND(A208=A207,A208&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6632,7 +6642,7 @@
       </c>
       <c r="D209" s="5"/>
       <c r="E209" t="str">
-        <f>IF(AND(A209=A208,A209&lt;&gt;""),1,"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
@@ -6647,7 +6657,7 @@
         <v>292</v>
       </c>
       <c r="E210" t="str">
-        <f>IF(AND(A210=A209,A210&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E210:E241" si="7">IF(AND(A210=A209,A210&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -6662,7 +6672,7 @@
         <v>300</v>
       </c>
       <c r="E211" t="str">
-        <f>IF(AND(A211=A210,A211&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6677,7 +6687,7 @@
         <v>292</v>
       </c>
       <c r="E212" t="str">
-        <f>IF(AND(A212=A211,A212&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6692,7 +6702,7 @@
         <v>182</v>
       </c>
       <c r="E213" t="str">
-        <f>IF(AND(A213=A212,A213&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6707,7 +6717,7 @@
         <v>593</v>
       </c>
       <c r="E214" t="str">
-        <f>IF(AND(A214=A213,A214&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6723,7 +6733,7 @@
       </c>
       <c r="D215" s="5"/>
       <c r="E215" t="str">
-        <f>IF(AND(A215=A214,A215&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6741,7 +6751,7 @@
         <v>302</v>
       </c>
       <c r="E216">
-        <f>IF(AND(A216=A215,A216&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -6759,7 +6769,7 @@
         <v>302</v>
       </c>
       <c r="E217">
-        <f>IF(AND(A217=A216,A217&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -6774,7 +6784,7 @@
         <v>290</v>
       </c>
       <c r="E218" t="str">
-        <f>IF(AND(A218=A217,A218&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6789,7 +6799,7 @@
         <v>290</v>
       </c>
       <c r="E219" t="str">
-        <f>IF(AND(A219=A218,A219&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6805,7 +6815,7 @@
       </c>
       <c r="D220" s="5"/>
       <c r="E220" t="str">
-        <f>IF(AND(A220=A219,A220&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6821,7 +6831,7 @@
       </c>
       <c r="D221" s="5"/>
       <c r="E221" t="str">
-        <f>IF(AND(A221=A220,A221&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6836,7 +6846,7 @@
         <v>300</v>
       </c>
       <c r="E222" t="str">
-        <f>IF(AND(A222=A221,A222&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6851,7 +6861,7 @@
         <v>292</v>
       </c>
       <c r="E223" t="str">
-        <f>IF(AND(A223=A222,A223&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6866,7 +6876,7 @@
         <v>290</v>
       </c>
       <c r="E224" t="str">
-        <f>IF(AND(A224=A223,A224&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6882,7 +6892,7 @@
       </c>
       <c r="D225" s="5"/>
       <c r="E225" t="str">
-        <f>IF(AND(A225=A224,A225&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6898,7 +6908,7 @@
       </c>
       <c r="D226" s="5"/>
       <c r="E226" t="str">
-        <f>IF(AND(A226=A225,A226&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6913,7 +6923,7 @@
         <v>300</v>
       </c>
       <c r="E227" t="str">
-        <f>IF(AND(A227=A226,A227&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6929,7 +6939,7 @@
       </c>
       <c r="D228" s="5"/>
       <c r="E228" t="str">
-        <f>IF(AND(A228=A227,A228&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6944,7 +6954,7 @@
         <v>290</v>
       </c>
       <c r="E229" t="str">
-        <f>IF(AND(A229=A228,A229&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6959,7 +6969,7 @@
         <v>300</v>
       </c>
       <c r="E230" t="str">
-        <f>IF(AND(A230=A229,A230&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6975,7 +6985,7 @@
       </c>
       <c r="D231" s="5"/>
       <c r="E231" t="str">
-        <f>IF(AND(A231=A230,A231&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6991,7 +7001,7 @@
       </c>
       <c r="D232" s="5"/>
       <c r="E232" t="str">
-        <f>IF(AND(A232=A231,A232&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7006,7 +7016,7 @@
         <v>593</v>
       </c>
       <c r="E233" t="str">
-        <f>IF(AND(A233=A232,A233&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7022,7 +7032,7 @@
       </c>
       <c r="D234" s="5"/>
       <c r="E234" t="str">
-        <f>IF(AND(A234=A233,A234&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7040,7 +7050,7 @@
         <v>131</v>
       </c>
       <c r="E235">
-        <f>IF(AND(A235=A234,A235&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -7056,7 +7066,7 @@
       </c>
       <c r="D236" s="5"/>
       <c r="E236" t="str">
-        <f>IF(AND(A236=A235,A236&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7071,7 +7081,7 @@
         <v>300</v>
       </c>
       <c r="E237" t="str">
-        <f>IF(AND(A237=A236,A237&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7086,7 +7096,7 @@
         <v>441</v>
       </c>
       <c r="E238" t="str">
-        <f>IF(AND(A238=A237,A238&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7101,7 +7111,7 @@
         <v>300</v>
       </c>
       <c r="E239" t="str">
-        <f>IF(AND(A239=A238,A239&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7117,7 +7127,7 @@
       </c>
       <c r="D240" s="5"/>
       <c r="E240" t="str">
-        <f>IF(AND(A240=A239,A240&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7132,7 +7142,7 @@
         <v>593</v>
       </c>
       <c r="E241" t="str">
-        <f>IF(AND(A241=A240,A241&lt;&gt;""),1,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7147,7 +7157,7 @@
         <v>292</v>
       </c>
       <c r="E242" t="str">
-        <f>IF(AND(A242=A241,A242&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E242:E252" si="8">IF(AND(A242=A241,A242&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -7162,7 +7172,7 @@
         <v>292</v>
       </c>
       <c r="E243" t="str">
-        <f>IF(AND(A243=A242,A243&lt;&gt;""),1,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -7177,7 +7187,7 @@
         <v>300</v>
       </c>
       <c r="E244" t="str">
-        <f>IF(AND(A244=A243,A244&lt;&gt;""),1,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -7192,7 +7202,7 @@
         <v>292</v>
       </c>
       <c r="E245" t="str">
-        <f>IF(AND(A245=A244,A245&lt;&gt;""),1,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -7207,7 +7217,7 @@
         <v>300</v>
       </c>
       <c r="E246" t="str">
-        <f>IF(AND(A246=A245,A246&lt;&gt;""),1,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -7222,7 +7232,7 @@
         <v>300</v>
       </c>
       <c r="E247" t="str">
-        <f>IF(AND(A247=A246,A247&lt;&gt;""),1,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -7237,7 +7247,7 @@
         <v>292</v>
       </c>
       <c r="E248" t="str">
-        <f>IF(AND(A248=A247,A248&lt;&gt;""),1,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -7252,7 +7262,7 @@
         <v>300</v>
       </c>
       <c r="E249" t="str">
-        <f>IF(AND(A249=A248,A249&lt;&gt;""),1,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -7267,7 +7277,7 @@
         <v>423</v>
       </c>
       <c r="E250" t="str">
-        <f>IF(AND(A250=A249,A250&lt;&gt;""),1,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -7283,7 +7293,7 @@
       </c>
       <c r="D251" s="5"/>
       <c r="E251" t="str">
-        <f>IF(AND(A251=A250,A251&lt;&gt;""),1,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -7301,7 +7311,7 @@
         <v>159</v>
       </c>
       <c r="E252">
-        <f>IF(AND(A252=A251,A252&lt;&gt;""),1,"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -7325,7 +7335,7 @@
         <v>423</v>
       </c>
       <c r="E254" t="str">
-        <f>IF(AND(A254=A253,A254&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E254:E270" si="9">IF(AND(A254=A253,A254&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -7340,7 +7350,7 @@
         <v>292</v>
       </c>
       <c r="E255" t="str">
-        <f>IF(AND(A255=A254,A255&lt;&gt;""),1,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7355,7 +7365,7 @@
         <v>292</v>
       </c>
       <c r="E256" t="str">
-        <f>IF(AND(A256=A255,A256&lt;&gt;""),1,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7370,7 +7380,7 @@
         <v>292</v>
       </c>
       <c r="E257" t="str">
-        <f>IF(AND(A257=A256,A257&lt;&gt;""),1,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7385,7 +7395,7 @@
         <v>290</v>
       </c>
       <c r="E258" t="str">
-        <f>IF(AND(A258=A257,A258&lt;&gt;""),1,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7400,7 +7410,7 @@
         <v>290</v>
       </c>
       <c r="E259" t="str">
-        <f>IF(AND(A259=A258,A259&lt;&gt;""),1,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7415,7 +7425,7 @@
         <v>290</v>
       </c>
       <c r="E260" t="str">
-        <f>IF(AND(A260=A259,A260&lt;&gt;""),1,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7430,7 +7440,7 @@
         <v>290</v>
       </c>
       <c r="E261" t="str">
-        <f>IF(AND(A261=A260,A261&lt;&gt;""),1,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7445,7 +7455,7 @@
         <v>300</v>
       </c>
       <c r="E262" t="str">
-        <f>IF(AND(A262=A261,A262&lt;&gt;""),1,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7460,7 +7470,7 @@
         <v>292</v>
       </c>
       <c r="E263" t="str">
-        <f>IF(AND(A263=A262,A263&lt;&gt;""),1,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7475,7 +7485,7 @@
         <v>593</v>
       </c>
       <c r="E264" t="str">
-        <f>IF(AND(A264=A263,A264&lt;&gt;""),1,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7490,7 +7500,7 @@
         <v>301</v>
       </c>
       <c r="E265" t="str">
-        <f>IF(AND(A265=A264,A265&lt;&gt;""),1,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7505,7 +7515,7 @@
         <v>301</v>
       </c>
       <c r="E266" t="str">
-        <f>IF(AND(A266=A265,A266&lt;&gt;""),1,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7520,7 +7530,7 @@
         <v>292</v>
       </c>
       <c r="E267" t="str">
-        <f>IF(AND(A267=A266,A267&lt;&gt;""),1,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7535,7 +7545,7 @@
         <v>292</v>
       </c>
       <c r="E268" t="str">
-        <f>IF(AND(A268=A267,A268&lt;&gt;""),1,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7551,7 +7561,7 @@
       </c>
       <c r="D269" s="5"/>
       <c r="E269" t="str">
-        <f>IF(AND(A269=A268,A269&lt;&gt;""),1,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7566,7 +7576,7 @@
         <v>292</v>
       </c>
       <c r="E270" t="str">
-        <f>IF(AND(A270=A269,A270&lt;&gt;""),1,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7597,7 +7607,7 @@
         <v>292</v>
       </c>
       <c r="E272" t="str">
-        <f>IF(AND(A272=A271,A272&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E272:E335" si="10">IF(AND(A272=A271,A272&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -7612,7 +7622,7 @@
         <v>300</v>
       </c>
       <c r="E273" t="str">
-        <f>IF(AND(A273=A272,A273&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7627,7 +7637,7 @@
         <v>300</v>
       </c>
       <c r="E274" t="str">
-        <f>IF(AND(A274=A273,A274&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7643,7 +7653,7 @@
       </c>
       <c r="D275" s="5"/>
       <c r="E275" t="str">
-        <f>IF(AND(A275=A274,A275&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7658,7 +7668,7 @@
         <v>292</v>
       </c>
       <c r="E276" t="str">
-        <f>IF(AND(A276=A275,A276&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7673,7 +7683,7 @@
         <v>292</v>
       </c>
       <c r="E277" t="str">
-        <f>IF(AND(A277=A276,A277&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7688,7 +7698,7 @@
         <v>292</v>
       </c>
       <c r="E278" t="str">
-        <f>IF(AND(A278=A277,A278&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7703,7 +7713,7 @@
         <v>300</v>
       </c>
       <c r="E279" t="str">
-        <f>IF(AND(A279=A278,A279&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7718,7 +7728,7 @@
         <v>300</v>
       </c>
       <c r="E280" t="str">
-        <f>IF(AND(A280=A279,A280&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7733,7 +7743,7 @@
         <v>300</v>
       </c>
       <c r="E281" t="str">
-        <f>IF(AND(A281=A280,A281&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7748,7 +7758,7 @@
         <v>300</v>
       </c>
       <c r="E282" t="str">
-        <f>IF(AND(A282=A281,A282&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7764,7 +7774,7 @@
       </c>
       <c r="D283" s="5"/>
       <c r="E283" t="str">
-        <f>IF(AND(A283=A282,A283&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7779,7 +7789,7 @@
         <v>292</v>
       </c>
       <c r="E284" t="str">
-        <f>IF(AND(A284=A283,A284&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7794,7 +7804,7 @@
         <v>292</v>
       </c>
       <c r="E285" t="str">
-        <f>IF(AND(A285=A284,A285&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7809,7 +7819,7 @@
         <v>292</v>
       </c>
       <c r="E286" t="str">
-        <f>IF(AND(A286=A285,A286&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7824,7 +7834,7 @@
         <v>292</v>
       </c>
       <c r="E287" t="str">
-        <f>IF(AND(A287=A286,A287&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7839,7 +7849,7 @@
         <v>441</v>
       </c>
       <c r="E288" t="str">
-        <f>IF(AND(A288=A287,A288&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7854,7 +7864,7 @@
         <v>292</v>
       </c>
       <c r="E289" t="str">
-        <f>IF(AND(A289=A288,A289&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7869,7 +7879,7 @@
         <v>290</v>
       </c>
       <c r="E290" t="str">
-        <f>IF(AND(A290=A289,A290&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7884,7 +7894,7 @@
         <v>593</v>
       </c>
       <c r="E291">
-        <f>IF(AND(A291=A290,A291&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -7899,7 +7909,7 @@
         <v>300</v>
       </c>
       <c r="E292" t="str">
-        <f>IF(AND(A292=A291,A292&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7914,7 +7924,7 @@
         <v>300</v>
       </c>
       <c r="E293" t="str">
-        <f>IF(AND(A293=A292,A293&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7929,7 +7939,7 @@
         <v>300</v>
       </c>
       <c r="E294" t="str">
-        <f>IF(AND(A294=A293,A294&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7944,7 +7954,7 @@
         <v>300</v>
       </c>
       <c r="E295" t="str">
-        <f>IF(AND(A295=A294,A295&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7959,7 +7969,7 @@
         <v>300</v>
       </c>
       <c r="E296" t="str">
-        <f>IF(AND(A296=A295,A296&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7974,7 +7984,7 @@
         <v>300</v>
       </c>
       <c r="E297" t="str">
-        <f>IF(AND(A297=A296,A297&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -7989,7 +7999,7 @@
         <v>290</v>
       </c>
       <c r="E298" t="str">
-        <f>IF(AND(A298=A297,A298&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8007,7 +8017,7 @@
         <v>774</v>
       </c>
       <c r="E299" t="str">
-        <f>IF(AND(A299=A298,A299&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8022,7 +8032,7 @@
         <v>300</v>
       </c>
       <c r="E300" t="str">
-        <f>IF(AND(A300=A299,A300&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8037,7 +8047,7 @@
         <v>593</v>
       </c>
       <c r="E301" t="str">
-        <f>IF(AND(A301=A300,A301&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8052,7 +8062,7 @@
         <v>423</v>
       </c>
       <c r="E302" t="str">
-        <f>IF(AND(A302=A301,A302&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8067,7 +8077,7 @@
         <v>292</v>
       </c>
       <c r="E303" t="str">
-        <f>IF(AND(A303=A302,A303&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8082,7 +8092,7 @@
         <v>300</v>
       </c>
       <c r="E304" t="str">
-        <f>IF(AND(A304=A303,A304&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8097,7 +8107,7 @@
         <v>292</v>
       </c>
       <c r="E305" t="str">
-        <f>IF(AND(A305=A304,A305&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8112,7 +8122,7 @@
         <v>292</v>
       </c>
       <c r="E306" t="str">
-        <f>IF(AND(A306=A305,A306&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8127,7 +8137,7 @@
         <v>290</v>
       </c>
       <c r="E307" t="str">
-        <f>IF(AND(A307=A306,A307&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8143,7 +8153,7 @@
       </c>
       <c r="D308" s="5"/>
       <c r="E308" t="str">
-        <f>IF(AND(A308=A307,A308&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8158,7 +8168,7 @@
         <v>423</v>
       </c>
       <c r="E309">
-        <f>IF(AND(A309=A308,A309&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -8176,7 +8186,7 @@
         <v>727</v>
       </c>
       <c r="E310">
-        <f>IF(AND(A310=A309,A310&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -8191,7 +8201,7 @@
         <v>292</v>
       </c>
       <c r="E311" t="str">
-        <f>IF(AND(A311=A310,A311&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8206,7 +8216,7 @@
         <v>290</v>
       </c>
       <c r="E312" t="str">
-        <f>IF(AND(A312=A311,A312&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8222,7 +8232,7 @@
       </c>
       <c r="D313" s="5"/>
       <c r="E313" t="str">
-        <f>IF(AND(A313=A312,A313&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8237,7 +8247,7 @@
         <v>300</v>
       </c>
       <c r="E314" t="str">
-        <f>IF(AND(A314=A313,A314&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8252,7 +8262,7 @@
         <v>292</v>
       </c>
       <c r="E315" t="str">
-        <f>IF(AND(A315=A314,A315&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8268,7 +8278,7 @@
       </c>
       <c r="D316" s="5"/>
       <c r="E316" t="str">
-        <f>IF(AND(A316=A315,A316&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8283,7 +8293,7 @@
         <v>292</v>
       </c>
       <c r="E317" t="str">
-        <f>IF(AND(A317=A316,A317&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8299,7 +8309,7 @@
       </c>
       <c r="D318" s="5"/>
       <c r="E318" t="str">
-        <f>IF(AND(A318=A317,A318&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8315,7 +8325,7 @@
       </c>
       <c r="D319" s="5"/>
       <c r="E319">
-        <f>IF(AND(A319=A318,A319&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -8331,7 +8341,7 @@
       </c>
       <c r="D320" s="5"/>
       <c r="E320" t="str">
-        <f>IF(AND(A320=A319,A320&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8346,7 +8356,7 @@
         <v>441</v>
       </c>
       <c r="E321" t="str">
-        <f>IF(AND(A321=A320,A321&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8362,7 +8372,7 @@
       </c>
       <c r="D322" s="5"/>
       <c r="E322" t="str">
-        <f>IF(AND(A322=A321,A322&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8377,7 +8387,7 @@
         <v>593</v>
       </c>
       <c r="E323" t="str">
-        <f>IF(AND(A323=A322,A323&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8392,7 +8402,7 @@
         <v>593</v>
       </c>
       <c r="E324" t="str">
-        <f>IF(AND(A324=A323,A324&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8407,7 +8417,7 @@
         <v>292</v>
       </c>
       <c r="E325" t="str">
-        <f>IF(AND(A325=A324,A325&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8422,7 +8432,7 @@
         <v>300</v>
       </c>
       <c r="E326" t="str">
-        <f>IF(AND(A326=A325,A326&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8437,7 +8447,7 @@
         <v>292</v>
       </c>
       <c r="E327" t="str">
-        <f>IF(AND(A327=A326,A327&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8452,7 +8462,7 @@
         <v>292</v>
       </c>
       <c r="E328" t="str">
-        <f>IF(AND(A328=A327,A328&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8467,7 +8477,7 @@
         <v>300</v>
       </c>
       <c r="E329" t="str">
-        <f>IF(AND(A329=A328,A329&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8483,7 +8493,7 @@
       </c>
       <c r="D330" s="5"/>
       <c r="E330" t="str">
-        <f>IF(AND(A330=A329,A330&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8498,7 +8508,7 @@
         <v>292</v>
       </c>
       <c r="E331" t="str">
-        <f>IF(AND(A331=A330,A331&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8513,7 +8523,7 @@
         <v>292</v>
       </c>
       <c r="E332" t="str">
-        <f>IF(AND(A332=A331,A332&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8528,7 +8538,7 @@
         <v>290</v>
       </c>
       <c r="E333" t="str">
-        <f>IF(AND(A333=A332,A333&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8544,7 +8554,7 @@
       </c>
       <c r="D334" s="5"/>
       <c r="E334" t="str">
-        <f>IF(AND(A334=A333,A334&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8559,7 +8569,7 @@
         <v>292</v>
       </c>
       <c r="E335" t="str">
-        <f>IF(AND(A335=A334,A335&lt;&gt;""),1,"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8574,7 +8584,7 @@
         <v>292</v>
       </c>
       <c r="E336" t="str">
-        <f>IF(AND(A336=A335,A336&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E336:E399" si="11">IF(AND(A336=A335,A336&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -8589,7 +8599,7 @@
         <v>423</v>
       </c>
       <c r="E337" t="str">
-        <f>IF(AND(A337=A336,A337&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8605,7 +8615,7 @@
       </c>
       <c r="D338" s="5"/>
       <c r="E338" t="str">
-        <f>IF(AND(A338=A337,A338&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8620,7 +8630,7 @@
         <v>593</v>
       </c>
       <c r="E339" t="str">
-        <f>IF(AND(A339=A338,A339&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8636,7 +8646,7 @@
       </c>
       <c r="D340" s="5"/>
       <c r="E340" t="str">
-        <f>IF(AND(A340=A339,A340&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8651,7 +8661,7 @@
         <v>292</v>
       </c>
       <c r="E341" t="str">
-        <f>IF(AND(A341=A340,A341&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8666,7 +8676,7 @@
         <v>292</v>
       </c>
       <c r="E342" t="str">
-        <f>IF(AND(A342=A341,A342&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8681,7 +8691,7 @@
         <v>292</v>
       </c>
       <c r="E343" t="str">
-        <f>IF(AND(A343=A342,A343&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8696,7 +8706,7 @@
         <v>292</v>
       </c>
       <c r="E344" t="str">
-        <f>IF(AND(A344=A343,A344&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8711,7 +8721,7 @@
         <v>292</v>
       </c>
       <c r="E345" t="str">
-        <f>IF(AND(A345=A344,A345&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8726,7 +8736,7 @@
         <v>292</v>
       </c>
       <c r="E346">
-        <f>IF(AND(A346=A345,A346&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -8742,7 +8752,7 @@
       </c>
       <c r="D347" s="5"/>
       <c r="E347" t="str">
-        <f>IF(AND(A347=A346,A347&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8757,7 +8767,7 @@
         <v>300</v>
       </c>
       <c r="E348" t="str">
-        <f>IF(AND(A348=A347,A348&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8772,7 +8782,7 @@
         <v>300</v>
       </c>
       <c r="E349" t="str">
-        <f>IF(AND(A349=A348,A349&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8788,7 +8798,7 @@
       </c>
       <c r="D350" s="5"/>
       <c r="E350" t="str">
-        <f>IF(AND(A350=A349,A350&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8803,7 +8813,7 @@
         <v>292</v>
       </c>
       <c r="E351" t="str">
-        <f>IF(AND(A351=A350,A351&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8818,7 +8828,7 @@
         <v>292</v>
       </c>
       <c r="E352" t="str">
-        <f>IF(AND(A352=A351,A352&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8834,11 +8844,11 @@
       </c>
       <c r="D353" s="5"/>
       <c r="E353" t="str">
-        <f>IF(AND(A353=A352,A353&lt;&gt;""),1,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="354" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="11" t="s">
         <v>574</v>
       </c>
@@ -8849,7 +8859,7 @@
         <v>593</v>
       </c>
       <c r="E354">
-        <f>IF(AND(A354=A353,A354&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -8864,7 +8874,7 @@
         <v>290</v>
       </c>
       <c r="E355" t="str">
-        <f>IF(AND(A355=A354,A355&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8879,7 +8889,7 @@
         <v>290</v>
       </c>
       <c r="E356" t="str">
-        <f>IF(AND(A356=A355,A356&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8895,11 +8905,11 @@
       </c>
       <c r="D357" s="5"/>
       <c r="E357" t="str">
-        <f>IF(AND(A357=A356,A357&lt;&gt;""),1,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+    </row>
+    <row r="358" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A358" s="6" t="s">
         <v>1</v>
       </c>
@@ -8913,7 +8923,7 @@
         <v>134</v>
       </c>
       <c r="E358">
-        <f>IF(AND(A358=A357,A358&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -8928,7 +8938,7 @@
         <v>290</v>
       </c>
       <c r="E359" t="str">
-        <f>IF(AND(A359=A358,A359&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8943,7 +8953,7 @@
         <v>290</v>
       </c>
       <c r="E360" t="str">
-        <f>IF(AND(A360=A359,A360&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8958,7 +8968,7 @@
         <v>290</v>
       </c>
       <c r="E361" t="str">
-        <f>IF(AND(A361=A360,A361&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8973,7 +8983,7 @@
         <v>290</v>
       </c>
       <c r="E362" t="str">
-        <f>IF(AND(A362=A361,A362&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8989,7 +8999,7 @@
       </c>
       <c r="D363" s="5"/>
       <c r="E363" t="str">
-        <f>IF(AND(A363=A362,A363&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9004,7 +9014,7 @@
         <v>300</v>
       </c>
       <c r="E364" t="str">
-        <f>IF(AND(A364=A363,A364&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9020,7 +9030,7 @@
       </c>
       <c r="D365" s="5"/>
       <c r="E365" t="str">
-        <f>IF(AND(A365=A364,A365&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9038,7 +9048,7 @@
         <v>155</v>
       </c>
       <c r="E366">
-        <f>IF(AND(A366=A365,A366&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -9053,7 +9063,7 @@
         <v>423</v>
       </c>
       <c r="E367">
-        <f>IF(AND(A367=A366,A367&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -9068,7 +9078,7 @@
         <v>593</v>
       </c>
       <c r="E368" t="str">
-        <f>IF(AND(A368=A367,A368&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9083,7 +9093,7 @@
         <v>292</v>
       </c>
       <c r="E369" t="str">
-        <f>IF(AND(A369=A368,A369&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9098,7 +9108,7 @@
         <v>300</v>
       </c>
       <c r="E370" t="str">
-        <f>IF(AND(A370=A369,A370&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9113,7 +9123,7 @@
         <v>300</v>
       </c>
       <c r="E371" t="str">
-        <f>IF(AND(A371=A370,A371&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9129,7 +9139,7 @@
       </c>
       <c r="D372" s="5"/>
       <c r="E372" t="str">
-        <f>IF(AND(A372=A371,A372&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9144,7 +9154,7 @@
         <v>292</v>
       </c>
       <c r="E373" t="str">
-        <f>IF(AND(A373=A372,A373&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9159,7 +9169,7 @@
         <v>299</v>
       </c>
       <c r="E374" t="str">
-        <f>IF(AND(A374=A373,A374&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9174,7 +9184,7 @@
         <v>292</v>
       </c>
       <c r="E375" t="str">
-        <f>IF(AND(A375=A374,A375&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9189,7 +9199,7 @@
         <v>292</v>
       </c>
       <c r="E376" t="str">
-        <f>IF(AND(A376=A375,A376&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9205,7 +9215,7 @@
       </c>
       <c r="D377" s="5"/>
       <c r="E377" t="str">
-        <f>IF(AND(A377=A376,A377&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9220,7 +9230,7 @@
         <v>292</v>
       </c>
       <c r="E378" t="str">
-        <f>IF(AND(A378=A377,A378&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9235,7 +9245,7 @@
         <v>156</v>
       </c>
       <c r="E379" t="str">
-        <f>IF(AND(A379=A378,A379&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9250,7 +9260,7 @@
         <v>300</v>
       </c>
       <c r="E380" t="str">
-        <f>IF(AND(A380=A379,A380&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9265,7 +9275,7 @@
         <v>292</v>
       </c>
       <c r="E381" t="str">
-        <f>IF(AND(A381=A380,A381&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9280,7 +9290,7 @@
         <v>300</v>
       </c>
       <c r="E382" t="str">
-        <f>IF(AND(A382=A381,A382&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9295,7 +9305,7 @@
         <v>300</v>
       </c>
       <c r="E383" t="str">
-        <f>IF(AND(A383=A382,A383&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9311,7 +9321,7 @@
       </c>
       <c r="D384" s="5"/>
       <c r="E384" t="str">
-        <f>IF(AND(A384=A383,A384&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9326,7 +9336,7 @@
         <v>292</v>
       </c>
       <c r="E385" t="str">
-        <f>IF(AND(A385=A384,A385&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9341,7 +9351,7 @@
         <v>292</v>
       </c>
       <c r="E386" t="str">
-        <f>IF(AND(A386=A385,A386&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9357,7 +9367,7 @@
       </c>
       <c r="D387" s="5"/>
       <c r="E387" t="str">
-        <f>IF(AND(A387=A386,A387&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9372,7 +9382,7 @@
         <v>593</v>
       </c>
       <c r="E388" t="str">
-        <f>IF(AND(A388=A387,A388&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9387,7 +9397,7 @@
         <v>593</v>
       </c>
       <c r="E389" t="str">
-        <f>IF(AND(A389=A388,A389&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9402,7 +9412,7 @@
         <v>292</v>
       </c>
       <c r="E390" t="str">
-        <f>IF(AND(A390=A389,A390&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9417,7 +9427,7 @@
         <v>300</v>
       </c>
       <c r="E391" t="str">
-        <f>IF(AND(A391=A390,A391&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9432,7 +9442,7 @@
         <v>292</v>
       </c>
       <c r="E392" t="str">
-        <f>IF(AND(A392=A391,A392&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9447,7 +9457,7 @@
         <v>292</v>
       </c>
       <c r="E393" t="str">
-        <f>IF(AND(A393=A392,A393&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9462,7 +9472,7 @@
         <v>292</v>
       </c>
       <c r="E394" t="str">
-        <f>IF(AND(A394=A393,A394&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9478,7 +9488,7 @@
       </c>
       <c r="D395" s="5"/>
       <c r="E395" t="str">
-        <f>IF(AND(A395=A394,A395&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9493,7 +9503,7 @@
         <v>441</v>
       </c>
       <c r="E396" t="str">
-        <f>IF(AND(A396=A395,A396&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9511,7 +9521,7 @@
         <v>243</v>
       </c>
       <c r="E397" t="str">
-        <f>IF(AND(A397=A396,A397&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9526,7 +9536,7 @@
         <v>292</v>
       </c>
       <c r="E398" t="str">
-        <f>IF(AND(A398=A397,A398&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9541,7 +9551,7 @@
         <v>300</v>
       </c>
       <c r="E399" t="str">
-        <f>IF(AND(A399=A398,A399&lt;&gt;""),1,"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9556,7 +9566,7 @@
         <v>292</v>
       </c>
       <c r="E400" t="str">
-        <f>IF(AND(A400=A399,A400&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E400:E463" si="12">IF(AND(A400=A399,A400&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -9571,7 +9581,7 @@
         <v>290</v>
       </c>
       <c r="E401" t="str">
-        <f>IF(AND(A401=A400,A401&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9587,7 +9597,7 @@
       </c>
       <c r="D402" s="5"/>
       <c r="E402" t="str">
-        <f>IF(AND(A402=A401,A402&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9602,7 +9612,7 @@
         <v>290</v>
       </c>
       <c r="E403" t="str">
-        <f>IF(AND(A403=A402,A403&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9617,7 +9627,7 @@
         <v>593</v>
       </c>
       <c r="E404" t="str">
-        <f>IF(AND(A404=A403,A404&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9632,7 +9642,7 @@
         <v>290</v>
       </c>
       <c r="E405" t="str">
-        <f>IF(AND(A405=A404,A405&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9647,7 +9657,7 @@
         <v>292</v>
       </c>
       <c r="E406" t="str">
-        <f>IF(AND(A406=A405,A406&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9663,7 +9673,7 @@
       </c>
       <c r="D407" s="5"/>
       <c r="E407" t="str">
-        <f>IF(AND(A407=A406,A407&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9679,7 +9689,7 @@
       </c>
       <c r="D408" s="5"/>
       <c r="E408" t="str">
-        <f>IF(AND(A408=A407,A408&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9695,7 +9705,7 @@
       </c>
       <c r="D409" s="5"/>
       <c r="E409" t="str">
-        <f>IF(AND(A409=A408,A409&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9710,7 +9720,7 @@
         <v>290</v>
       </c>
       <c r="E410" t="str">
-        <f>IF(AND(A410=A409,A410&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9726,7 +9736,7 @@
       </c>
       <c r="D411" s="5"/>
       <c r="E411" t="str">
-        <f>IF(AND(A411=A410,A411&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9741,7 +9751,7 @@
         <v>290</v>
       </c>
       <c r="E412" t="str">
-        <f>IF(AND(A412=A411,A412&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9759,7 +9769,7 @@
         <v>155</v>
       </c>
       <c r="E413" t="str">
-        <f>IF(AND(A413=A412,A413&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9774,7 +9784,7 @@
         <v>423</v>
       </c>
       <c r="E414" t="str">
-        <f>IF(AND(A414=A413,A414&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9790,7 +9800,7 @@
       </c>
       <c r="D415" s="5"/>
       <c r="E415" t="str">
-        <f>IF(AND(A415=A414,A415&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9808,7 +9818,7 @@
         <v>159</v>
       </c>
       <c r="E416">
-        <f>IF(AND(A416=A415,A416&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -9826,11 +9836,11 @@
         <v>155</v>
       </c>
       <c r="E417">
-        <f>IF(AND(A417=A416,A417&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" s="5" t="s">
         <v>266</v>
       </c>
@@ -9842,7 +9852,7 @@
       </c>
       <c r="D418" s="5"/>
       <c r="E418" t="str">
-        <f>IF(AND(A418=A417,A418&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9860,7 +9870,7 @@
         <v>159</v>
       </c>
       <c r="E419">
-        <f>IF(AND(A419=A418,A419&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -9878,7 +9888,7 @@
         <v>155</v>
       </c>
       <c r="E420">
-        <f>IF(AND(A420=A419,A420&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -9888,7 +9898,7 @@
         <v>156</v>
       </c>
       <c r="E421" t="str">
-        <f>IF(AND(A421=A420,A421&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9898,7 +9908,7 @@
         <v>156</v>
       </c>
       <c r="E422" t="str">
-        <f>IF(AND(A422=A421,A422&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9908,7 +9918,7 @@
         <v>156</v>
       </c>
       <c r="E423" t="str">
-        <f>IF(AND(A423=A422,A423&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9918,7 +9928,7 @@
         <v>156</v>
       </c>
       <c r="E424" t="str">
-        <f>IF(AND(A424=A423,A424&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9928,7 +9938,7 @@
         <v>156</v>
       </c>
       <c r="E425" t="str">
-        <f>IF(AND(A425=A424,A425&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9938,7 +9948,7 @@
         <v>156</v>
       </c>
       <c r="E426" t="str">
-        <f>IF(AND(A426=A425,A426&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9948,7 +9958,7 @@
         <v>156</v>
       </c>
       <c r="E427" t="str">
-        <f>IF(AND(A427=A426,A427&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9958,7 +9968,7 @@
         <v>156</v>
       </c>
       <c r="E428" t="str">
-        <f>IF(AND(A428=A427,A428&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9968,7 +9978,7 @@
         <v>156</v>
       </c>
       <c r="E429" t="str">
-        <f>IF(AND(A429=A428,A429&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9978,7 +9988,7 @@
         <v>156</v>
       </c>
       <c r="E430" t="str">
-        <f>IF(AND(A430=A429,A430&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9988,7 +9998,7 @@
         <v>156</v>
       </c>
       <c r="E431" t="str">
-        <f>IF(AND(A431=A430,A431&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9998,7 +10008,7 @@
         <v>156</v>
       </c>
       <c r="E432" t="str">
-        <f>IF(AND(A432=A431,A432&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10008,7 +10018,7 @@
         <v>156</v>
       </c>
       <c r="E433" t="str">
-        <f>IF(AND(A433=A432,A433&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10018,7 +10028,7 @@
         <v>156</v>
       </c>
       <c r="E434" t="str">
-        <f>IF(AND(A434=A433,A434&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10028,7 +10038,7 @@
         <v>156</v>
       </c>
       <c r="E435" t="str">
-        <f>IF(AND(A435=A434,A435&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10038,7 +10048,7 @@
         <v>156</v>
       </c>
       <c r="E436" t="str">
-        <f>IF(AND(A436=A435,A436&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10048,7 +10058,7 @@
         <v>156</v>
       </c>
       <c r="E437" t="str">
-        <f>IF(AND(A437=A436,A437&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10058,7 +10068,7 @@
         <v>156</v>
       </c>
       <c r="E438" t="str">
-        <f>IF(AND(A438=A437,A438&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10068,7 +10078,7 @@
         <v>156</v>
       </c>
       <c r="E439" t="str">
-        <f>IF(AND(A439=A438,A439&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10078,7 +10088,7 @@
         <v>156</v>
       </c>
       <c r="E440" t="str">
-        <f>IF(AND(A440=A439,A440&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10088,7 +10098,7 @@
         <v>156</v>
       </c>
       <c r="E441" t="str">
-        <f>IF(AND(A441=A440,A441&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10098,7 +10108,7 @@
         <v>156</v>
       </c>
       <c r="E442" t="str">
-        <f>IF(AND(A442=A441,A442&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10108,7 +10118,7 @@
         <v>156</v>
       </c>
       <c r="E443" t="str">
-        <f>IF(AND(A443=A442,A443&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10118,7 +10128,7 @@
         <v>156</v>
       </c>
       <c r="E444" t="str">
-        <f>IF(AND(A444=A443,A444&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10128,7 +10138,7 @@
         <v>156</v>
       </c>
       <c r="E445" t="str">
-        <f>IF(AND(A445=A444,A445&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10138,7 +10148,7 @@
         <v>156</v>
       </c>
       <c r="E446" t="str">
-        <f>IF(AND(A446=A445,A446&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10148,7 +10158,7 @@
         <v>156</v>
       </c>
       <c r="E447" t="str">
-        <f>IF(AND(A447=A446,A447&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10158,7 +10168,7 @@
         <v>156</v>
       </c>
       <c r="E448" t="str">
-        <f>IF(AND(A448=A447,A448&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10168,7 +10178,7 @@
         <v>156</v>
       </c>
       <c r="E449" t="str">
-        <f>IF(AND(A449=A448,A449&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10178,7 +10188,7 @@
         <v>156</v>
       </c>
       <c r="E450" t="str">
-        <f>IF(AND(A450=A449,A450&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10188,7 +10198,7 @@
         <v>156</v>
       </c>
       <c r="E451" t="str">
-        <f>IF(AND(A451=A450,A451&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10198,7 +10208,7 @@
         <v>156</v>
       </c>
       <c r="E452" t="str">
-        <f>IF(AND(A452=A451,A452&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10208,7 +10218,7 @@
         <v>156</v>
       </c>
       <c r="E453" t="str">
-        <f>IF(AND(A453=A452,A453&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10218,7 +10228,7 @@
         <v>156</v>
       </c>
       <c r="E454" t="str">
-        <f>IF(AND(A454=A453,A454&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10228,7 +10238,7 @@
         <v>156</v>
       </c>
       <c r="E455" t="str">
-        <f>IF(AND(A455=A454,A455&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10238,7 +10248,7 @@
         <v>156</v>
       </c>
       <c r="E456" t="str">
-        <f>IF(AND(A456=A455,A456&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10248,7 +10258,7 @@
         <v>156</v>
       </c>
       <c r="E457" t="str">
-        <f>IF(AND(A457=A456,A457&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10258,7 +10268,7 @@
         <v>156</v>
       </c>
       <c r="E458" t="str">
-        <f>IF(AND(A458=A457,A458&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10268,7 +10278,7 @@
         <v>156</v>
       </c>
       <c r="E459" t="str">
-        <f>IF(AND(A459=A458,A459&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10278,7 +10288,7 @@
         <v>156</v>
       </c>
       <c r="E460" t="str">
-        <f>IF(AND(A460=A459,A460&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10288,7 +10298,7 @@
         <v>156</v>
       </c>
       <c r="E461" t="str">
-        <f>IF(AND(A461=A460,A461&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10298,7 +10308,7 @@
         <v>156</v>
       </c>
       <c r="E462" t="str">
-        <f>IF(AND(A462=A461,A462&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10308,7 +10318,7 @@
         <v>156</v>
       </c>
       <c r="E463" t="str">
-        <f>IF(AND(A463=A462,A463&lt;&gt;""),1,"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -10318,7 +10328,7 @@
         <v>156</v>
       </c>
       <c r="E464" t="str">
-        <f>IF(AND(A464=A463,A464&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E464:E527" si="13">IF(AND(A464=A463,A464&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -10328,7 +10338,7 @@
         <v>156</v>
       </c>
       <c r="E465" t="str">
-        <f>IF(AND(A465=A464,A465&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10338,7 +10348,7 @@
         <v>156</v>
       </c>
       <c r="E466" t="str">
-        <f>IF(AND(A466=A465,A466&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10348,7 +10358,7 @@
         <v>156</v>
       </c>
       <c r="E467" t="str">
-        <f>IF(AND(A467=A466,A467&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10358,7 +10368,7 @@
         <v>156</v>
       </c>
       <c r="E468" t="str">
-        <f>IF(AND(A468=A467,A468&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10368,7 +10378,7 @@
         <v>156</v>
       </c>
       <c r="E469" t="str">
-        <f>IF(AND(A469=A468,A469&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10378,7 +10388,7 @@
         <v>156</v>
       </c>
       <c r="E470" t="str">
-        <f>IF(AND(A470=A469,A470&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10388,7 +10398,7 @@
         <v>156</v>
       </c>
       <c r="E471" t="str">
-        <f>IF(AND(A471=A470,A471&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10398,7 +10408,7 @@
         <v>156</v>
       </c>
       <c r="E472" t="str">
-        <f>IF(AND(A472=A471,A472&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10408,7 +10418,7 @@
         <v>156</v>
       </c>
       <c r="E473" t="str">
-        <f>IF(AND(A473=A472,A473&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10418,7 +10428,7 @@
         <v>156</v>
       </c>
       <c r="E474" t="str">
-        <f>IF(AND(A474=A473,A474&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10428,7 +10438,7 @@
         <v>156</v>
       </c>
       <c r="E475" t="str">
-        <f>IF(AND(A475=A474,A475&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10438,7 +10448,7 @@
         <v>156</v>
       </c>
       <c r="E476" t="str">
-        <f>IF(AND(A476=A475,A476&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10448,7 +10458,7 @@
         <v>156</v>
       </c>
       <c r="E477" t="str">
-        <f>IF(AND(A477=A476,A477&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10458,7 +10468,7 @@
         <v>156</v>
       </c>
       <c r="E478" t="str">
-        <f>IF(AND(A478=A477,A478&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10468,7 +10478,7 @@
         <v>156</v>
       </c>
       <c r="E479" t="str">
-        <f>IF(AND(A479=A478,A479&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10478,7 +10488,7 @@
         <v>156</v>
       </c>
       <c r="E480" t="str">
-        <f>IF(AND(A480=A479,A480&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10488,7 +10498,7 @@
         <v>156</v>
       </c>
       <c r="E481" t="str">
-        <f>IF(AND(A481=A480,A481&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10498,7 +10508,7 @@
         <v>156</v>
       </c>
       <c r="E482" t="str">
-        <f>IF(AND(A482=A481,A482&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10508,7 +10518,7 @@
         <v>156</v>
       </c>
       <c r="E483" t="str">
-        <f>IF(AND(A483=A482,A483&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10518,7 +10528,7 @@
         <v>156</v>
       </c>
       <c r="E484" t="str">
-        <f>IF(AND(A484=A483,A484&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10528,7 +10538,7 @@
         <v>156</v>
       </c>
       <c r="E485" t="str">
-        <f>IF(AND(A485=A484,A485&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10538,7 +10548,7 @@
         <v>156</v>
       </c>
       <c r="E486" t="str">
-        <f>IF(AND(A486=A485,A486&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10548,7 +10558,7 @@
         <v>156</v>
       </c>
       <c r="E487" t="str">
-        <f>IF(AND(A487=A486,A487&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10558,7 +10568,7 @@
         <v>156</v>
       </c>
       <c r="E488" t="str">
-        <f>IF(AND(A488=A487,A488&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10568,7 +10578,7 @@
         <v>156</v>
       </c>
       <c r="E489" t="str">
-        <f>IF(AND(A489=A488,A489&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10578,7 +10588,7 @@
         <v>156</v>
       </c>
       <c r="E490" t="str">
-        <f>IF(AND(A490=A489,A490&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10588,7 +10598,7 @@
         <v>156</v>
       </c>
       <c r="E491" t="str">
-        <f>IF(AND(A491=A490,A491&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10598,7 +10608,7 @@
         <v>156</v>
       </c>
       <c r="E492" t="str">
-        <f>IF(AND(A492=A491,A492&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10608,7 +10618,7 @@
         <v>156</v>
       </c>
       <c r="E493" t="str">
-        <f>IF(AND(A493=A492,A493&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10618,7 +10628,7 @@
         <v>156</v>
       </c>
       <c r="E494" t="str">
-        <f>IF(AND(A494=A493,A494&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10628,7 +10638,7 @@
         <v>156</v>
       </c>
       <c r="E495" t="str">
-        <f>IF(AND(A495=A494,A495&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10638,7 +10648,7 @@
         <v>156</v>
       </c>
       <c r="E496" t="str">
-        <f>IF(AND(A496=A495,A496&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10648,7 +10658,7 @@
         <v>156</v>
       </c>
       <c r="E497" t="str">
-        <f>IF(AND(A497=A496,A497&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10658,7 +10668,7 @@
         <v>156</v>
       </c>
       <c r="E498" t="str">
-        <f>IF(AND(A498=A497,A498&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10668,7 +10678,7 @@
         <v>156</v>
       </c>
       <c r="E499" t="str">
-        <f>IF(AND(A499=A498,A499&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10678,7 +10688,7 @@
         <v>156</v>
       </c>
       <c r="E500" t="str">
-        <f>IF(AND(A500=A499,A500&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10688,7 +10698,7 @@
         <v>156</v>
       </c>
       <c r="E501" t="str">
-        <f>IF(AND(A501=A500,A501&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10698,7 +10708,7 @@
         <v>156</v>
       </c>
       <c r="E502" t="str">
-        <f>IF(AND(A502=A501,A502&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10708,7 +10718,7 @@
         <v>156</v>
       </c>
       <c r="E503" t="str">
-        <f>IF(AND(A503=A502,A503&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10718,7 +10728,7 @@
         <v>156</v>
       </c>
       <c r="E504" t="str">
-        <f>IF(AND(A504=A503,A504&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10728,7 +10738,7 @@
         <v>156</v>
       </c>
       <c r="E505" t="str">
-        <f>IF(AND(A505=A504,A505&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10738,7 +10748,7 @@
         <v>156</v>
       </c>
       <c r="E506" t="str">
-        <f>IF(AND(A506=A505,A506&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10748,7 +10758,7 @@
         <v>156</v>
       </c>
       <c r="E507" t="str">
-        <f>IF(AND(A507=A506,A507&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10758,7 +10768,7 @@
         <v>156</v>
       </c>
       <c r="E508" t="str">
-        <f>IF(AND(A508=A507,A508&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10768,7 +10778,7 @@
         <v>156</v>
       </c>
       <c r="E509" t="str">
-        <f>IF(AND(A509=A508,A509&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10778,7 +10788,7 @@
         <v>156</v>
       </c>
       <c r="E510" t="str">
-        <f>IF(AND(A510=A509,A510&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10788,7 +10798,7 @@
         <v>156</v>
       </c>
       <c r="E511" t="str">
-        <f>IF(AND(A511=A510,A511&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10798,7 +10808,7 @@
         <v>156</v>
       </c>
       <c r="E512" t="str">
-        <f>IF(AND(A512=A511,A512&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10808,7 +10818,7 @@
         <v>156</v>
       </c>
       <c r="E513" t="str">
-        <f>IF(AND(A513=A512,A513&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10818,7 +10828,7 @@
         <v>156</v>
       </c>
       <c r="E514" t="str">
-        <f>IF(AND(A514=A513,A514&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10828,7 +10838,7 @@
         <v>156</v>
       </c>
       <c r="E515" t="str">
-        <f>IF(AND(A515=A514,A515&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10838,7 +10848,7 @@
         <v>156</v>
       </c>
       <c r="E516" t="str">
-        <f>IF(AND(A516=A515,A516&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10848,7 +10858,7 @@
         <v>156</v>
       </c>
       <c r="E517" t="str">
-        <f>IF(AND(A517=A516,A517&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10858,7 +10868,7 @@
         <v>156</v>
       </c>
       <c r="E518" t="str">
-        <f>IF(AND(A518=A517,A518&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10868,7 +10878,7 @@
         <v>156</v>
       </c>
       <c r="E519" t="str">
-        <f>IF(AND(A519=A518,A519&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10878,7 +10888,7 @@
         <v>156</v>
       </c>
       <c r="E520" t="str">
-        <f>IF(AND(A520=A519,A520&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10888,7 +10898,7 @@
         <v>156</v>
       </c>
       <c r="E521" t="str">
-        <f>IF(AND(A521=A520,A521&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10898,7 +10908,7 @@
         <v>156</v>
       </c>
       <c r="E522" t="str">
-        <f>IF(AND(A522=A521,A522&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10908,7 +10918,7 @@
         <v>156</v>
       </c>
       <c r="E523" t="str">
-        <f>IF(AND(A523=A522,A523&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10918,7 +10928,7 @@
         <v>156</v>
       </c>
       <c r="E524" t="str">
-        <f>IF(AND(A524=A523,A524&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10928,7 +10938,7 @@
         <v>156</v>
       </c>
       <c r="E525" t="str">
-        <f>IF(AND(A525=A524,A525&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10938,7 +10948,7 @@
         <v>156</v>
       </c>
       <c r="E526" t="str">
-        <f>IF(AND(A526=A525,A526&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10948,7 +10958,7 @@
         <v>156</v>
       </c>
       <c r="E527" t="str">
-        <f>IF(AND(A527=A526,A527&lt;&gt;""),1,"")</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10958,7 +10968,7 @@
         <v>156</v>
       </c>
       <c r="E528" t="str">
-        <f>IF(AND(A528=A527,A528&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E528:E591" si="14">IF(AND(A528=A527,A528&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -10968,7 +10978,7 @@
         <v>156</v>
       </c>
       <c r="E529" t="str">
-        <f>IF(AND(A529=A528,A529&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -10978,7 +10988,7 @@
         <v>156</v>
       </c>
       <c r="E530" t="str">
-        <f>IF(AND(A530=A529,A530&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -10988,7 +10998,7 @@
         <v>156</v>
       </c>
       <c r="E531" t="str">
-        <f>IF(AND(A531=A530,A531&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -10998,7 +11008,7 @@
         <v>156</v>
       </c>
       <c r="E532" t="str">
-        <f>IF(AND(A532=A531,A532&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11008,7 +11018,7 @@
         <v>156</v>
       </c>
       <c r="E533" t="str">
-        <f>IF(AND(A533=A532,A533&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11018,7 +11028,7 @@
         <v>156</v>
       </c>
       <c r="E534" t="str">
-        <f>IF(AND(A534=A533,A534&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11028,7 +11038,7 @@
         <v>156</v>
       </c>
       <c r="E535" t="str">
-        <f>IF(AND(A535=A534,A535&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11038,7 +11048,7 @@
         <v>156</v>
       </c>
       <c r="E536" t="str">
-        <f>IF(AND(A536=A535,A536&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11048,7 +11058,7 @@
         <v>156</v>
       </c>
       <c r="E537" t="str">
-        <f>IF(AND(A537=A536,A537&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11058,7 +11068,7 @@
         <v>156</v>
       </c>
       <c r="E538" t="str">
-        <f>IF(AND(A538=A537,A538&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11068,7 +11078,7 @@
         <v>156</v>
       </c>
       <c r="E539" t="str">
-        <f>IF(AND(A539=A538,A539&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11078,7 +11088,7 @@
         <v>156</v>
       </c>
       <c r="E540" t="str">
-        <f>IF(AND(A540=A539,A540&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11088,7 +11098,7 @@
         <v>156</v>
       </c>
       <c r="E541" t="str">
-        <f>IF(AND(A541=A540,A541&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11098,7 +11108,7 @@
         <v>156</v>
       </c>
       <c r="E542" t="str">
-        <f>IF(AND(A542=A541,A542&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11108,7 +11118,7 @@
         <v>156</v>
       </c>
       <c r="E543" t="str">
-        <f>IF(AND(A543=A542,A543&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11118,7 +11128,7 @@
         <v>156</v>
       </c>
       <c r="E544" t="str">
-        <f>IF(AND(A544=A543,A544&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11128,7 +11138,7 @@
         <v>156</v>
       </c>
       <c r="E545" t="str">
-        <f>IF(AND(A545=A544,A545&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11138,7 +11148,7 @@
         <v>156</v>
       </c>
       <c r="E546" t="str">
-        <f>IF(AND(A546=A545,A546&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11148,7 +11158,7 @@
         <v>156</v>
       </c>
       <c r="E547" t="str">
-        <f>IF(AND(A547=A546,A547&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11158,7 +11168,7 @@
         <v>156</v>
       </c>
       <c r="E548" t="str">
-        <f>IF(AND(A548=A547,A548&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11168,7 +11178,7 @@
         <v>156</v>
       </c>
       <c r="E549" t="str">
-        <f>IF(AND(A549=A548,A549&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11178,7 +11188,7 @@
         <v>156</v>
       </c>
       <c r="E550" t="str">
-        <f>IF(AND(A550=A549,A550&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11188,7 +11198,7 @@
         <v>156</v>
       </c>
       <c r="E551" t="str">
-        <f>IF(AND(A551=A550,A551&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11198,7 +11208,7 @@
         <v>156</v>
       </c>
       <c r="E552" t="str">
-        <f>IF(AND(A552=A551,A552&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11208,7 +11218,7 @@
         <v>156</v>
       </c>
       <c r="E553" t="str">
-        <f>IF(AND(A553=A552,A553&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11218,7 +11228,7 @@
         <v>156</v>
       </c>
       <c r="E554" t="str">
-        <f>IF(AND(A554=A553,A554&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11228,7 +11238,7 @@
         <v>156</v>
       </c>
       <c r="E555" t="str">
-        <f>IF(AND(A555=A554,A555&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11238,7 +11248,7 @@
         <v>156</v>
       </c>
       <c r="E556" t="str">
-        <f>IF(AND(A556=A555,A556&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11248,7 +11258,7 @@
         <v>156</v>
       </c>
       <c r="E557" t="str">
-        <f>IF(AND(A557=A556,A557&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11258,7 +11268,7 @@
         <v>156</v>
       </c>
       <c r="E558" t="str">
-        <f>IF(AND(A558=A557,A558&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11268,7 +11278,7 @@
         <v>156</v>
       </c>
       <c r="E559" t="str">
-        <f>IF(AND(A559=A558,A559&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11278,7 +11288,7 @@
         <v>156</v>
       </c>
       <c r="E560" t="str">
-        <f>IF(AND(A560=A559,A560&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11288,7 +11298,7 @@
         <v>156</v>
       </c>
       <c r="E561" t="str">
-        <f>IF(AND(A561=A560,A561&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11298,7 +11308,7 @@
         <v>156</v>
       </c>
       <c r="E562" t="str">
-        <f>IF(AND(A562=A561,A562&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11308,7 +11318,7 @@
         <v>156</v>
       </c>
       <c r="E563" t="str">
-        <f>IF(AND(A563=A562,A563&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11318,7 +11328,7 @@
         <v>156</v>
       </c>
       <c r="E564" t="str">
-        <f>IF(AND(A564=A563,A564&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11328,7 +11338,7 @@
         <v>156</v>
       </c>
       <c r="E565" t="str">
-        <f>IF(AND(A565=A564,A565&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11338,7 +11348,7 @@
         <v>156</v>
       </c>
       <c r="E566" t="str">
-        <f>IF(AND(A566=A565,A566&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11348,7 +11358,7 @@
         <v>156</v>
       </c>
       <c r="E567" t="str">
-        <f>IF(AND(A567=A566,A567&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11358,7 +11368,7 @@
         <v>156</v>
       </c>
       <c r="E568" t="str">
-        <f>IF(AND(A568=A567,A568&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11368,7 +11378,7 @@
         <v>156</v>
       </c>
       <c r="E569" t="str">
-        <f>IF(AND(A569=A568,A569&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11378,7 +11388,7 @@
         <v>156</v>
       </c>
       <c r="E570" t="str">
-        <f>IF(AND(A570=A569,A570&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11388,7 +11398,7 @@
         <v>156</v>
       </c>
       <c r="E571" t="str">
-        <f>IF(AND(A571=A570,A571&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11398,7 +11408,7 @@
         <v>156</v>
       </c>
       <c r="E572" t="str">
-        <f>IF(AND(A572=A571,A572&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11408,7 +11418,7 @@
         <v>156</v>
       </c>
       <c r="E573" t="str">
-        <f>IF(AND(A573=A572,A573&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11418,7 +11428,7 @@
         <v>156</v>
       </c>
       <c r="E574" t="str">
-        <f>IF(AND(A574=A573,A574&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11428,7 +11438,7 @@
         <v>156</v>
       </c>
       <c r="E575" t="str">
-        <f>IF(AND(A575=A574,A575&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11438,7 +11448,7 @@
         <v>156</v>
       </c>
       <c r="E576" t="str">
-        <f>IF(AND(A576=A575,A576&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11448,7 +11458,7 @@
         <v>156</v>
       </c>
       <c r="E577" t="str">
-        <f>IF(AND(A577=A576,A577&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11458,7 +11468,7 @@
         <v>156</v>
       </c>
       <c r="E578" t="str">
-        <f>IF(AND(A578=A577,A578&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11468,7 +11478,7 @@
         <v>156</v>
       </c>
       <c r="E579" t="str">
-        <f>IF(AND(A579=A578,A579&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11478,7 +11488,7 @@
         <v>156</v>
       </c>
       <c r="E580" t="str">
-        <f>IF(AND(A580=A579,A580&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11488,7 +11498,7 @@
         <v>156</v>
       </c>
       <c r="E581" t="str">
-        <f>IF(AND(A581=A580,A581&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11498,7 +11508,7 @@
         <v>156</v>
       </c>
       <c r="E582" t="str">
-        <f>IF(AND(A582=A581,A582&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11508,7 +11518,7 @@
         <v>156</v>
       </c>
       <c r="E583" t="str">
-        <f>IF(AND(A583=A582,A583&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11518,7 +11528,7 @@
         <v>156</v>
       </c>
       <c r="E584" t="str">
-        <f>IF(AND(A584=A583,A584&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11528,7 +11538,7 @@
         <v>156</v>
       </c>
       <c r="E585" t="str">
-        <f>IF(AND(A585=A584,A585&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11538,7 +11548,7 @@
         <v>156</v>
       </c>
       <c r="E586" t="str">
-        <f>IF(AND(A586=A585,A586&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11548,7 +11558,7 @@
         <v>156</v>
       </c>
       <c r="E587" t="str">
-        <f>IF(AND(A587=A586,A587&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11558,7 +11568,7 @@
         <v>156</v>
       </c>
       <c r="E588" t="str">
-        <f>IF(AND(A588=A587,A588&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11568,7 +11578,7 @@
         <v>156</v>
       </c>
       <c r="E589" t="str">
-        <f>IF(AND(A589=A588,A589&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11578,7 +11588,7 @@
         <v>156</v>
       </c>
       <c r="E590" t="str">
-        <f>IF(AND(A590=A589,A590&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11588,7 +11598,7 @@
         <v>156</v>
       </c>
       <c r="E591" t="str">
-        <f>IF(AND(A591=A590,A591&lt;&gt;""),1,"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -11598,7 +11608,7 @@
         <v>156</v>
       </c>
       <c r="E592" t="str">
-        <f>IF(AND(A592=A591,A592&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E592:E655" si="15">IF(AND(A592=A591,A592&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -11608,7 +11618,7 @@
         <v>156</v>
       </c>
       <c r="E593" t="str">
-        <f>IF(AND(A593=A592,A593&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11618,7 +11628,7 @@
         <v>156</v>
       </c>
       <c r="E594" t="str">
-        <f>IF(AND(A594=A593,A594&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11628,7 +11638,7 @@
         <v>156</v>
       </c>
       <c r="E595" t="str">
-        <f>IF(AND(A595=A594,A595&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11638,7 +11648,7 @@
         <v>156</v>
       </c>
       <c r="E596" t="str">
-        <f>IF(AND(A596=A595,A596&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11648,7 +11658,7 @@
         <v>156</v>
       </c>
       <c r="E597" t="str">
-        <f>IF(AND(A597=A596,A597&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11658,7 +11668,7 @@
         <v>156</v>
       </c>
       <c r="E598" t="str">
-        <f>IF(AND(A598=A597,A598&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11668,7 +11678,7 @@
         <v>156</v>
       </c>
       <c r="E599" t="str">
-        <f>IF(AND(A599=A598,A599&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11678,7 +11688,7 @@
         <v>156</v>
       </c>
       <c r="E600" t="str">
-        <f>IF(AND(A600=A599,A600&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11688,7 +11698,7 @@
         <v>156</v>
       </c>
       <c r="E601" t="str">
-        <f>IF(AND(A601=A600,A601&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11698,7 +11708,7 @@
         <v>156</v>
       </c>
       <c r="E602" t="str">
-        <f>IF(AND(A602=A601,A602&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11708,7 +11718,7 @@
         <v>156</v>
       </c>
       <c r="E603" t="str">
-        <f>IF(AND(A603=A602,A603&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11718,7 +11728,7 @@
         <v>156</v>
       </c>
       <c r="E604" t="str">
-        <f>IF(AND(A604=A603,A604&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11728,7 +11738,7 @@
         <v>156</v>
       </c>
       <c r="E605" t="str">
-        <f>IF(AND(A605=A604,A605&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11738,7 +11748,7 @@
         <v>156</v>
       </c>
       <c r="E606" t="str">
-        <f>IF(AND(A606=A605,A606&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11748,7 +11758,7 @@
         <v>156</v>
       </c>
       <c r="E607" t="str">
-        <f>IF(AND(A607=A606,A607&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11758,7 +11768,7 @@
         <v>156</v>
       </c>
       <c r="E608" t="str">
-        <f>IF(AND(A608=A607,A608&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11768,7 +11778,7 @@
         <v>156</v>
       </c>
       <c r="E609" t="str">
-        <f>IF(AND(A609=A608,A609&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11778,7 +11788,7 @@
         <v>156</v>
       </c>
       <c r="E610" t="str">
-        <f>IF(AND(A610=A609,A610&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11788,7 +11798,7 @@
         <v>156</v>
       </c>
       <c r="E611" t="str">
-        <f>IF(AND(A611=A610,A611&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11798,7 +11808,7 @@
         <v>156</v>
       </c>
       <c r="E612" t="str">
-        <f>IF(AND(A612=A611,A612&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11808,7 +11818,7 @@
         <v>156</v>
       </c>
       <c r="E613" t="str">
-        <f>IF(AND(A613=A612,A613&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11818,7 +11828,7 @@
         <v>156</v>
       </c>
       <c r="E614" t="str">
-        <f>IF(AND(A614=A613,A614&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11828,7 +11838,7 @@
         <v>156</v>
       </c>
       <c r="E615" t="str">
-        <f>IF(AND(A615=A614,A615&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11838,7 +11848,7 @@
         <v>156</v>
       </c>
       <c r="E616" t="str">
-        <f>IF(AND(A616=A615,A616&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11848,7 +11858,7 @@
         <v>156</v>
       </c>
       <c r="E617" t="str">
-        <f>IF(AND(A617=A616,A617&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11858,7 +11868,7 @@
         <v>156</v>
       </c>
       <c r="E618" t="str">
-        <f>IF(AND(A618=A617,A618&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11868,7 +11878,7 @@
         <v>156</v>
       </c>
       <c r="E619" t="str">
-        <f>IF(AND(A619=A618,A619&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11878,7 +11888,7 @@
         <v>156</v>
       </c>
       <c r="E620" t="str">
-        <f>IF(AND(A620=A619,A620&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11888,7 +11898,7 @@
         <v>156</v>
       </c>
       <c r="E621" t="str">
-        <f>IF(AND(A621=A620,A621&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11898,7 +11908,7 @@
         <v>156</v>
       </c>
       <c r="E622" t="str">
-        <f>IF(AND(A622=A621,A622&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11908,7 +11918,7 @@
         <v>156</v>
       </c>
       <c r="E623" t="str">
-        <f>IF(AND(A623=A622,A623&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11918,7 +11928,7 @@
         <v>156</v>
       </c>
       <c r="E624" t="str">
-        <f>IF(AND(A624=A623,A624&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11928,7 +11938,7 @@
         <v>156</v>
       </c>
       <c r="E625" t="str">
-        <f>IF(AND(A625=A624,A625&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11938,7 +11948,7 @@
         <v>156</v>
       </c>
       <c r="E626" t="str">
-        <f>IF(AND(A626=A625,A626&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11948,7 +11958,7 @@
         <v>156</v>
       </c>
       <c r="E627" t="str">
-        <f>IF(AND(A627=A626,A627&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11958,7 +11968,7 @@
         <v>156</v>
       </c>
       <c r="E628" t="str">
-        <f>IF(AND(A628=A627,A628&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11968,7 +11978,7 @@
         <v>156</v>
       </c>
       <c r="E629" t="str">
-        <f>IF(AND(A629=A628,A629&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11978,7 +11988,7 @@
         <v>156</v>
       </c>
       <c r="E630" t="str">
-        <f>IF(AND(A630=A629,A630&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11988,7 +11998,7 @@
         <v>156</v>
       </c>
       <c r="E631" t="str">
-        <f>IF(AND(A631=A630,A631&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -11998,7 +12008,7 @@
         <v>156</v>
       </c>
       <c r="E632" t="str">
-        <f>IF(AND(A632=A631,A632&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12008,7 +12018,7 @@
         <v>156</v>
       </c>
       <c r="E633" t="str">
-        <f>IF(AND(A633=A632,A633&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12018,7 +12028,7 @@
         <v>156</v>
       </c>
       <c r="E634" t="str">
-        <f>IF(AND(A634=A633,A634&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12028,7 +12038,7 @@
         <v>156</v>
       </c>
       <c r="E635" t="str">
-        <f>IF(AND(A635=A634,A635&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12038,7 +12048,7 @@
         <v>156</v>
       </c>
       <c r="E636" t="str">
-        <f>IF(AND(A636=A635,A636&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12048,7 +12058,7 @@
         <v>156</v>
       </c>
       <c r="E637" t="str">
-        <f>IF(AND(A637=A636,A637&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12058,7 +12068,7 @@
         <v>156</v>
       </c>
       <c r="E638" t="str">
-        <f>IF(AND(A638=A637,A638&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12068,7 +12078,7 @@
         <v>156</v>
       </c>
       <c r="E639" t="str">
-        <f>IF(AND(A639=A638,A639&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12078,7 +12088,7 @@
         <v>156</v>
       </c>
       <c r="E640" t="str">
-        <f>IF(AND(A640=A639,A640&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12088,7 +12098,7 @@
         <v>156</v>
       </c>
       <c r="E641" t="str">
-        <f>IF(AND(A641=A640,A641&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12098,7 +12108,7 @@
         <v>156</v>
       </c>
       <c r="E642" t="str">
-        <f>IF(AND(A642=A641,A642&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12108,7 +12118,7 @@
         <v>156</v>
       </c>
       <c r="E643" t="str">
-        <f>IF(AND(A643=A642,A643&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12118,7 +12128,7 @@
         <v>156</v>
       </c>
       <c r="E644" t="str">
-        <f>IF(AND(A644=A643,A644&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12128,7 +12138,7 @@
         <v>156</v>
       </c>
       <c r="E645" t="str">
-        <f>IF(AND(A645=A644,A645&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12138,7 +12148,7 @@
         <v>156</v>
       </c>
       <c r="E646" t="str">
-        <f>IF(AND(A646=A645,A646&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12148,7 +12158,7 @@
         <v>156</v>
       </c>
       <c r="E647" t="str">
-        <f>IF(AND(A647=A646,A647&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12158,7 +12168,7 @@
         <v>156</v>
       </c>
       <c r="E648" t="str">
-        <f>IF(AND(A648=A647,A648&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12168,7 +12178,7 @@
         <v>156</v>
       </c>
       <c r="E649" t="str">
-        <f>IF(AND(A649=A648,A649&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12178,7 +12188,7 @@
         <v>156</v>
       </c>
       <c r="E650" t="str">
-        <f>IF(AND(A650=A649,A650&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12188,7 +12198,7 @@
         <v>156</v>
       </c>
       <c r="E651" t="str">
-        <f>IF(AND(A651=A650,A651&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12198,7 +12208,7 @@
         <v>156</v>
       </c>
       <c r="E652" t="str">
-        <f>IF(AND(A652=A651,A652&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12208,7 +12218,7 @@
         <v>156</v>
       </c>
       <c r="E653" t="str">
-        <f>IF(AND(A653=A652,A653&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12218,7 +12228,7 @@
         <v>156</v>
       </c>
       <c r="E654" t="str">
-        <f>IF(AND(A654=A653,A654&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12228,7 +12238,7 @@
         <v>156</v>
       </c>
       <c r="E655" t="str">
-        <f>IF(AND(A655=A654,A655&lt;&gt;""),1,"")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12238,7 +12248,7 @@
         <v>156</v>
       </c>
       <c r="E656" t="str">
-        <f>IF(AND(A656=A655,A656&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E656:E719" si="16">IF(AND(A656=A655,A656&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -12248,7 +12258,7 @@
         <v>156</v>
       </c>
       <c r="E657" t="str">
-        <f>IF(AND(A657=A656,A657&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12258,7 +12268,7 @@
         <v>156</v>
       </c>
       <c r="E658" t="str">
-        <f>IF(AND(A658=A657,A658&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12268,7 +12278,7 @@
         <v>156</v>
       </c>
       <c r="E659" t="str">
-        <f>IF(AND(A659=A658,A659&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12278,7 +12288,7 @@
         <v>156</v>
       </c>
       <c r="E660" t="str">
-        <f>IF(AND(A660=A659,A660&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12288,7 +12298,7 @@
         <v>156</v>
       </c>
       <c r="E661" t="str">
-        <f>IF(AND(A661=A660,A661&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12298,7 +12308,7 @@
         <v>156</v>
       </c>
       <c r="E662" t="str">
-        <f>IF(AND(A662=A661,A662&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12308,7 +12318,7 @@
         <v>156</v>
       </c>
       <c r="E663" t="str">
-        <f>IF(AND(A663=A662,A663&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12318,7 +12328,7 @@
         <v>156</v>
       </c>
       <c r="E664" t="str">
-        <f>IF(AND(A664=A663,A664&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12328,7 +12338,7 @@
         <v>156</v>
       </c>
       <c r="E665" t="str">
-        <f>IF(AND(A665=A664,A665&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12338,7 +12348,7 @@
         <v>156</v>
       </c>
       <c r="E666" t="str">
-        <f>IF(AND(A666=A665,A666&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12348,7 +12358,7 @@
         <v>156</v>
       </c>
       <c r="E667" t="str">
-        <f>IF(AND(A667=A666,A667&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12358,7 +12368,7 @@
         <v>156</v>
       </c>
       <c r="E668" t="str">
-        <f>IF(AND(A668=A667,A668&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12368,7 +12378,7 @@
         <v>156</v>
       </c>
       <c r="E669" t="str">
-        <f>IF(AND(A669=A668,A669&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12378,7 +12388,7 @@
         <v>156</v>
       </c>
       <c r="E670" t="str">
-        <f>IF(AND(A670=A669,A670&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12388,7 +12398,7 @@
         <v>156</v>
       </c>
       <c r="E671" t="str">
-        <f>IF(AND(A671=A670,A671&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12398,7 +12408,7 @@
         <v>156</v>
       </c>
       <c r="E672" t="str">
-        <f>IF(AND(A672=A671,A672&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12408,7 +12418,7 @@
         <v>156</v>
       </c>
       <c r="E673" t="str">
-        <f>IF(AND(A673=A672,A673&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12418,7 +12428,7 @@
         <v>156</v>
       </c>
       <c r="E674" t="str">
-        <f>IF(AND(A674=A673,A674&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12428,7 +12438,7 @@
         <v>156</v>
       </c>
       <c r="E675" t="str">
-        <f>IF(AND(A675=A674,A675&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12438,7 +12448,7 @@
         <v>156</v>
       </c>
       <c r="E676" t="str">
-        <f>IF(AND(A676=A675,A676&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12448,7 +12458,7 @@
         <v>156</v>
       </c>
       <c r="E677" t="str">
-        <f>IF(AND(A677=A676,A677&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12458,7 +12468,7 @@
         <v>156</v>
       </c>
       <c r="E678" t="str">
-        <f>IF(AND(A678=A677,A678&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12468,7 +12478,7 @@
         <v>156</v>
       </c>
       <c r="E679" t="str">
-        <f>IF(AND(A679=A678,A679&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12478,7 +12488,7 @@
         <v>156</v>
       </c>
       <c r="E680" t="str">
-        <f>IF(AND(A680=A679,A680&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12488,7 +12498,7 @@
         <v>156</v>
       </c>
       <c r="E681" t="str">
-        <f>IF(AND(A681=A680,A681&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12498,7 +12508,7 @@
         <v>156</v>
       </c>
       <c r="E682" t="str">
-        <f>IF(AND(A682=A681,A682&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12508,7 +12518,7 @@
         <v>156</v>
       </c>
       <c r="E683" t="str">
-        <f>IF(AND(A683=A682,A683&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12518,7 +12528,7 @@
         <v>156</v>
       </c>
       <c r="E684" t="str">
-        <f>IF(AND(A684=A683,A684&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12528,7 +12538,7 @@
         <v>156</v>
       </c>
       <c r="E685" t="str">
-        <f>IF(AND(A685=A684,A685&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12538,7 +12548,7 @@
         <v>156</v>
       </c>
       <c r="E686" t="str">
-        <f>IF(AND(A686=A685,A686&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12548,7 +12558,7 @@
         <v>156</v>
       </c>
       <c r="E687" t="str">
-        <f>IF(AND(A687=A686,A687&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12558,7 +12568,7 @@
         <v>156</v>
       </c>
       <c r="E688" t="str">
-        <f>IF(AND(A688=A687,A688&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12568,7 +12578,7 @@
         <v>156</v>
       </c>
       <c r="E689" t="str">
-        <f>IF(AND(A689=A688,A689&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12578,7 +12588,7 @@
         <v>156</v>
       </c>
       <c r="E690" t="str">
-        <f>IF(AND(A690=A689,A690&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12588,7 +12598,7 @@
         <v>156</v>
       </c>
       <c r="E691" t="str">
-        <f>IF(AND(A691=A690,A691&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12598,7 +12608,7 @@
         <v>156</v>
       </c>
       <c r="E692" t="str">
-        <f>IF(AND(A692=A691,A692&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12608,7 +12618,7 @@
         <v>156</v>
       </c>
       <c r="E693" t="str">
-        <f>IF(AND(A693=A692,A693&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12618,7 +12628,7 @@
         <v>156</v>
       </c>
       <c r="E694" t="str">
-        <f>IF(AND(A694=A693,A694&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12628,7 +12638,7 @@
         <v>156</v>
       </c>
       <c r="E695" t="str">
-        <f>IF(AND(A695=A694,A695&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12638,7 +12648,7 @@
         <v>156</v>
       </c>
       <c r="E696" t="str">
-        <f>IF(AND(A696=A695,A696&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12648,7 +12658,7 @@
         <v>156</v>
       </c>
       <c r="E697" t="str">
-        <f>IF(AND(A697=A696,A697&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12658,7 +12668,7 @@
         <v>156</v>
       </c>
       <c r="E698" t="str">
-        <f>IF(AND(A698=A697,A698&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12668,7 +12678,7 @@
         <v>156</v>
       </c>
       <c r="E699" t="str">
-        <f>IF(AND(A699=A698,A699&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12678,7 +12688,7 @@
         <v>156</v>
       </c>
       <c r="E700" t="str">
-        <f>IF(AND(A700=A699,A700&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12688,7 +12698,7 @@
         <v>156</v>
       </c>
       <c r="E701" t="str">
-        <f>IF(AND(A701=A700,A701&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12698,7 +12708,7 @@
         <v>156</v>
       </c>
       <c r="E702" t="str">
-        <f>IF(AND(A702=A701,A702&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12708,7 +12718,7 @@
         <v>156</v>
       </c>
       <c r="E703" t="str">
-        <f>IF(AND(A703=A702,A703&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12718,7 +12728,7 @@
         <v>156</v>
       </c>
       <c r="E704" t="str">
-        <f>IF(AND(A704=A703,A704&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12728,7 +12738,7 @@
         <v>156</v>
       </c>
       <c r="E705" t="str">
-        <f>IF(AND(A705=A704,A705&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12738,7 +12748,7 @@
         <v>156</v>
       </c>
       <c r="E706" t="str">
-        <f>IF(AND(A706=A705,A706&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12748,7 +12758,7 @@
         <v>156</v>
       </c>
       <c r="E707" t="str">
-        <f>IF(AND(A707=A706,A707&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12758,7 +12768,7 @@
         <v>156</v>
       </c>
       <c r="E708" t="str">
-        <f>IF(AND(A708=A707,A708&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12768,7 +12778,7 @@
         <v>156</v>
       </c>
       <c r="E709" t="str">
-        <f>IF(AND(A709=A708,A709&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12778,7 +12788,7 @@
         <v>156</v>
       </c>
       <c r="E710" t="str">
-        <f>IF(AND(A710=A709,A710&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12788,7 +12798,7 @@
         <v>156</v>
       </c>
       <c r="E711" t="str">
-        <f>IF(AND(A711=A710,A711&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12798,7 +12808,7 @@
         <v>156</v>
       </c>
       <c r="E712" t="str">
-        <f>IF(AND(A712=A711,A712&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12808,7 +12818,7 @@
         <v>156</v>
       </c>
       <c r="E713" t="str">
-        <f>IF(AND(A713=A712,A713&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12818,7 +12828,7 @@
         <v>156</v>
       </c>
       <c r="E714" t="str">
-        <f>IF(AND(A714=A713,A714&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12828,7 +12838,7 @@
         <v>156</v>
       </c>
       <c r="E715" t="str">
-        <f>IF(AND(A715=A714,A715&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12838,7 +12848,7 @@
         <v>156</v>
       </c>
       <c r="E716" t="str">
-        <f>IF(AND(A716=A715,A716&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12848,7 +12858,7 @@
         <v>156</v>
       </c>
       <c r="E717" t="str">
-        <f>IF(AND(A717=A716,A717&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12858,7 +12868,7 @@
         <v>156</v>
       </c>
       <c r="E718" t="str">
-        <f>IF(AND(A718=A717,A718&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12868,7 +12878,7 @@
         <v>156</v>
       </c>
       <c r="E719" t="str">
-        <f>IF(AND(A719=A718,A719&lt;&gt;""),1,"")</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12878,7 +12888,7 @@
         <v>156</v>
       </c>
       <c r="E720" t="str">
-        <f>IF(AND(A720=A719,A720&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E720:E783" si="17">IF(AND(A720=A719,A720&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -12888,7 +12898,7 @@
         <v>156</v>
       </c>
       <c r="E721" t="str">
-        <f>IF(AND(A721=A720,A721&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -12898,7 +12908,7 @@
         <v>156</v>
       </c>
       <c r="E722" t="str">
-        <f>IF(AND(A722=A721,A722&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -12908,7 +12918,7 @@
         <v>156</v>
       </c>
       <c r="E723" t="str">
-        <f>IF(AND(A723=A722,A723&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -12918,7 +12928,7 @@
         <v>156</v>
       </c>
       <c r="E724" t="str">
-        <f>IF(AND(A724=A723,A724&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -12928,7 +12938,7 @@
         <v>156</v>
       </c>
       <c r="E725" t="str">
-        <f>IF(AND(A725=A724,A725&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -12938,7 +12948,7 @@
         <v>156</v>
       </c>
       <c r="E726" t="str">
-        <f>IF(AND(A726=A725,A726&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -12948,7 +12958,7 @@
         <v>156</v>
       </c>
       <c r="E727" t="str">
-        <f>IF(AND(A727=A726,A727&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -12958,7 +12968,7 @@
         <v>156</v>
       </c>
       <c r="E728" t="str">
-        <f>IF(AND(A728=A727,A728&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -12968,7 +12978,7 @@
         <v>156</v>
       </c>
       <c r="E729" t="str">
-        <f>IF(AND(A729=A728,A729&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -12978,7 +12988,7 @@
         <v>156</v>
       </c>
       <c r="E730" t="str">
-        <f>IF(AND(A730=A729,A730&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -12988,7 +12998,7 @@
         <v>156</v>
       </c>
       <c r="E731" t="str">
-        <f>IF(AND(A731=A730,A731&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -12998,7 +13008,7 @@
         <v>156</v>
       </c>
       <c r="E732" t="str">
-        <f>IF(AND(A732=A731,A732&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13008,7 +13018,7 @@
         <v>156</v>
       </c>
       <c r="E733" t="str">
-        <f>IF(AND(A733=A732,A733&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13018,7 +13028,7 @@
         <v>156</v>
       </c>
       <c r="E734" t="str">
-        <f>IF(AND(A734=A733,A734&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13028,7 +13038,7 @@
         <v>156</v>
       </c>
       <c r="E735" t="str">
-        <f>IF(AND(A735=A734,A735&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13038,7 +13048,7 @@
         <v>156</v>
       </c>
       <c r="E736" t="str">
-        <f>IF(AND(A736=A735,A736&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13048,7 +13058,7 @@
         <v>156</v>
       </c>
       <c r="E737" t="str">
-        <f>IF(AND(A737=A736,A737&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13058,7 +13068,7 @@
         <v>156</v>
       </c>
       <c r="E738" t="str">
-        <f>IF(AND(A738=A737,A738&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13068,7 +13078,7 @@
         <v>156</v>
       </c>
       <c r="E739" t="str">
-        <f>IF(AND(A739=A738,A739&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13078,7 +13088,7 @@
         <v>156</v>
       </c>
       <c r="E740" t="str">
-        <f>IF(AND(A740=A739,A740&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13088,7 +13098,7 @@
         <v>156</v>
       </c>
       <c r="E741" t="str">
-        <f>IF(AND(A741=A740,A741&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13098,7 +13108,7 @@
         <v>156</v>
       </c>
       <c r="E742" t="str">
-        <f>IF(AND(A742=A741,A742&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13108,7 +13118,7 @@
         <v>156</v>
       </c>
       <c r="E743" t="str">
-        <f>IF(AND(A743=A742,A743&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13118,7 +13128,7 @@
         <v>156</v>
       </c>
       <c r="E744" t="str">
-        <f>IF(AND(A744=A743,A744&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13128,7 +13138,7 @@
         <v>156</v>
       </c>
       <c r="E745" t="str">
-        <f>IF(AND(A745=A744,A745&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13138,7 +13148,7 @@
         <v>156</v>
       </c>
       <c r="E746" t="str">
-        <f>IF(AND(A746=A745,A746&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13148,7 +13158,7 @@
         <v>156</v>
       </c>
       <c r="E747" t="str">
-        <f>IF(AND(A747=A746,A747&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13158,7 +13168,7 @@
         <v>156</v>
       </c>
       <c r="E748" t="str">
-        <f>IF(AND(A748=A747,A748&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13168,7 +13178,7 @@
         <v>156</v>
       </c>
       <c r="E749" t="str">
-        <f>IF(AND(A749=A748,A749&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13178,7 +13188,7 @@
         <v>156</v>
       </c>
       <c r="E750" t="str">
-        <f>IF(AND(A750=A749,A750&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13188,7 +13198,7 @@
         <v>156</v>
       </c>
       <c r="E751" t="str">
-        <f>IF(AND(A751=A750,A751&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13198,7 +13208,7 @@
         <v>156</v>
       </c>
       <c r="E752" t="str">
-        <f>IF(AND(A752=A751,A752&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13208,7 +13218,7 @@
         <v>156</v>
       </c>
       <c r="E753" t="str">
-        <f>IF(AND(A753=A752,A753&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13218,7 +13228,7 @@
         <v>156</v>
       </c>
       <c r="E754" t="str">
-        <f>IF(AND(A754=A753,A754&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13228,7 +13238,7 @@
         <v>156</v>
       </c>
       <c r="E755" t="str">
-        <f>IF(AND(A755=A754,A755&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13238,7 +13248,7 @@
         <v>156</v>
       </c>
       <c r="E756" t="str">
-        <f>IF(AND(A756=A755,A756&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13248,7 +13258,7 @@
         <v>156</v>
       </c>
       <c r="E757" t="str">
-        <f>IF(AND(A757=A756,A757&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13258,7 +13268,7 @@
         <v>156</v>
       </c>
       <c r="E758" t="str">
-        <f>IF(AND(A758=A757,A758&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13268,7 +13278,7 @@
         <v>156</v>
       </c>
       <c r="E759" t="str">
-        <f>IF(AND(A759=A758,A759&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13278,7 +13288,7 @@
         <v>156</v>
       </c>
       <c r="E760" t="str">
-        <f>IF(AND(A760=A759,A760&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13288,7 +13298,7 @@
         <v>156</v>
       </c>
       <c r="E761" t="str">
-        <f>IF(AND(A761=A760,A761&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13298,7 +13308,7 @@
         <v>156</v>
       </c>
       <c r="E762" t="str">
-        <f>IF(AND(A762=A761,A762&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13308,7 +13318,7 @@
         <v>156</v>
       </c>
       <c r="E763" t="str">
-        <f>IF(AND(A763=A762,A763&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13318,7 +13328,7 @@
         <v>156</v>
       </c>
       <c r="E764" t="str">
-        <f>IF(AND(A764=A763,A764&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13328,7 +13338,7 @@
         <v>156</v>
       </c>
       <c r="E765" t="str">
-        <f>IF(AND(A765=A764,A765&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13338,7 +13348,7 @@
         <v>156</v>
       </c>
       <c r="E766" t="str">
-        <f>IF(AND(A766=A765,A766&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13348,7 +13358,7 @@
         <v>156</v>
       </c>
       <c r="E767" t="str">
-        <f>IF(AND(A767=A766,A767&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13358,7 +13368,7 @@
         <v>156</v>
       </c>
       <c r="E768" t="str">
-        <f>IF(AND(A768=A767,A768&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13368,7 +13378,7 @@
         <v>156</v>
       </c>
       <c r="E769" t="str">
-        <f>IF(AND(A769=A768,A769&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13378,7 +13388,7 @@
         <v>156</v>
       </c>
       <c r="E770" t="str">
-        <f>IF(AND(A770=A769,A770&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13388,7 +13398,7 @@
         <v>156</v>
       </c>
       <c r="E771" t="str">
-        <f>IF(AND(A771=A770,A771&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13398,7 +13408,7 @@
         <v>156</v>
       </c>
       <c r="E772" t="str">
-        <f>IF(AND(A772=A771,A772&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13408,7 +13418,7 @@
         <v>156</v>
       </c>
       <c r="E773" t="str">
-        <f>IF(AND(A773=A772,A773&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13418,7 +13428,7 @@
         <v>156</v>
       </c>
       <c r="E774" t="str">
-        <f>IF(AND(A774=A773,A774&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13428,7 +13438,7 @@
         <v>156</v>
       </c>
       <c r="E775" t="str">
-        <f>IF(AND(A775=A774,A775&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13438,7 +13448,7 @@
         <v>156</v>
       </c>
       <c r="E776" t="str">
-        <f>IF(AND(A776=A775,A776&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13448,7 +13458,7 @@
         <v>156</v>
       </c>
       <c r="E777" t="str">
-        <f>IF(AND(A777=A776,A777&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13458,7 +13468,7 @@
         <v>156</v>
       </c>
       <c r="E778" t="str">
-        <f>IF(AND(A778=A777,A778&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13468,7 +13478,7 @@
         <v>156</v>
       </c>
       <c r="E779" t="str">
-        <f>IF(AND(A779=A778,A779&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13478,7 +13488,7 @@
         <v>156</v>
       </c>
       <c r="E780" t="str">
-        <f>IF(AND(A780=A779,A780&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13488,7 +13498,7 @@
         <v>156</v>
       </c>
       <c r="E781" t="str">
-        <f>IF(AND(A781=A780,A781&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13498,7 +13508,7 @@
         <v>156</v>
       </c>
       <c r="E782" t="str">
-        <f>IF(AND(A782=A781,A782&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13508,7 +13518,7 @@
         <v>156</v>
       </c>
       <c r="E783" t="str">
-        <f>IF(AND(A783=A782,A783&lt;&gt;""),1,"")</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -13518,7 +13528,7 @@
         <v>156</v>
       </c>
       <c r="E784" t="str">
-        <f>IF(AND(A784=A783,A784&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E784:E847" si="18">IF(AND(A784=A783,A784&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -13528,7 +13538,7 @@
         <v>156</v>
       </c>
       <c r="E785" t="str">
-        <f>IF(AND(A785=A784,A785&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13538,7 +13548,7 @@
         <v>156</v>
       </c>
       <c r="E786" t="str">
-        <f>IF(AND(A786=A785,A786&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13548,7 +13558,7 @@
         <v>156</v>
       </c>
       <c r="E787" t="str">
-        <f>IF(AND(A787=A786,A787&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13558,7 +13568,7 @@
         <v>156</v>
       </c>
       <c r="E788" t="str">
-        <f>IF(AND(A788=A787,A788&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13568,7 +13578,7 @@
         <v>156</v>
       </c>
       <c r="E789" t="str">
-        <f>IF(AND(A789=A788,A789&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13578,7 +13588,7 @@
         <v>156</v>
       </c>
       <c r="E790" t="str">
-        <f>IF(AND(A790=A789,A790&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13588,7 +13598,7 @@
         <v>156</v>
       </c>
       <c r="E791" t="str">
-        <f>IF(AND(A791=A790,A791&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13598,7 +13608,7 @@
         <v>156</v>
       </c>
       <c r="E792" t="str">
-        <f>IF(AND(A792=A791,A792&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13608,7 +13618,7 @@
         <v>156</v>
       </c>
       <c r="E793" t="str">
-        <f>IF(AND(A793=A792,A793&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13618,7 +13628,7 @@
         <v>156</v>
       </c>
       <c r="E794" t="str">
-        <f>IF(AND(A794=A793,A794&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13628,7 +13638,7 @@
         <v>156</v>
       </c>
       <c r="E795" t="str">
-        <f>IF(AND(A795=A794,A795&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13638,7 +13648,7 @@
         <v>156</v>
       </c>
       <c r="E796" t="str">
-        <f>IF(AND(A796=A795,A796&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13648,7 +13658,7 @@
         <v>156</v>
       </c>
       <c r="E797" t="str">
-        <f>IF(AND(A797=A796,A797&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13658,7 +13668,7 @@
         <v>156</v>
       </c>
       <c r="E798" t="str">
-        <f>IF(AND(A798=A797,A798&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13668,7 +13678,7 @@
         <v>156</v>
       </c>
       <c r="E799" t="str">
-        <f>IF(AND(A799=A798,A799&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13678,7 +13688,7 @@
         <v>156</v>
       </c>
       <c r="E800" t="str">
-        <f>IF(AND(A800=A799,A800&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13688,7 +13698,7 @@
         <v>156</v>
       </c>
       <c r="E801" t="str">
-        <f>IF(AND(A801=A800,A801&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13698,7 +13708,7 @@
         <v>156</v>
       </c>
       <c r="E802" t="str">
-        <f>IF(AND(A802=A801,A802&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13708,7 +13718,7 @@
         <v>156</v>
       </c>
       <c r="E803" t="str">
-        <f>IF(AND(A803=A802,A803&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13718,7 +13728,7 @@
         <v>156</v>
       </c>
       <c r="E804" t="str">
-        <f>IF(AND(A804=A803,A804&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13728,7 +13738,7 @@
         <v>156</v>
       </c>
       <c r="E805" t="str">
-        <f>IF(AND(A805=A804,A805&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13738,7 +13748,7 @@
         <v>156</v>
       </c>
       <c r="E806" t="str">
-        <f>IF(AND(A806=A805,A806&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13748,7 +13758,7 @@
         <v>156</v>
       </c>
       <c r="E807" t="str">
-        <f>IF(AND(A807=A806,A807&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13758,7 +13768,7 @@
         <v>156</v>
       </c>
       <c r="E808" t="str">
-        <f>IF(AND(A808=A807,A808&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13768,7 +13778,7 @@
         <v>156</v>
       </c>
       <c r="E809" t="str">
-        <f>IF(AND(A809=A808,A809&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13778,7 +13788,7 @@
         <v>156</v>
       </c>
       <c r="E810" t="str">
-        <f>IF(AND(A810=A809,A810&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13788,7 +13798,7 @@
         <v>156</v>
       </c>
       <c r="E811" t="str">
-        <f>IF(AND(A811=A810,A811&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13798,7 +13808,7 @@
         <v>156</v>
       </c>
       <c r="E812" t="str">
-        <f>IF(AND(A812=A811,A812&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13808,7 +13818,7 @@
         <v>156</v>
       </c>
       <c r="E813" t="str">
-        <f>IF(AND(A813=A812,A813&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13818,7 +13828,7 @@
         <v>156</v>
       </c>
       <c r="E814" t="str">
-        <f>IF(AND(A814=A813,A814&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13828,7 +13838,7 @@
         <v>156</v>
       </c>
       <c r="E815" t="str">
-        <f>IF(AND(A815=A814,A815&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13838,7 +13848,7 @@
         <v>156</v>
       </c>
       <c r="E816" t="str">
-        <f>IF(AND(A816=A815,A816&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13848,7 +13858,7 @@
         <v>156</v>
       </c>
       <c r="E817" t="str">
-        <f>IF(AND(A817=A816,A817&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13858,7 +13868,7 @@
         <v>156</v>
       </c>
       <c r="E818" t="str">
-        <f>IF(AND(A818=A817,A818&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13868,7 +13878,7 @@
         <v>156</v>
       </c>
       <c r="E819" t="str">
-        <f>IF(AND(A819=A818,A819&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13878,7 +13888,7 @@
         <v>156</v>
       </c>
       <c r="E820" t="str">
-        <f>IF(AND(A820=A819,A820&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13888,7 +13898,7 @@
         <v>156</v>
       </c>
       <c r="E821" t="str">
-        <f>IF(AND(A821=A820,A821&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13898,7 +13908,7 @@
         <v>156</v>
       </c>
       <c r="E822" t="str">
-        <f>IF(AND(A822=A821,A822&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13908,7 +13918,7 @@
         <v>156</v>
       </c>
       <c r="E823" t="str">
-        <f>IF(AND(A823=A822,A823&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13918,7 +13928,7 @@
         <v>156</v>
       </c>
       <c r="E824" t="str">
-        <f>IF(AND(A824=A823,A824&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13928,7 +13938,7 @@
         <v>156</v>
       </c>
       <c r="E825" t="str">
-        <f>IF(AND(A825=A824,A825&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13938,7 +13948,7 @@
         <v>156</v>
       </c>
       <c r="E826" t="str">
-        <f>IF(AND(A826=A825,A826&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13948,7 +13958,7 @@
         <v>156</v>
       </c>
       <c r="E827" t="str">
-        <f>IF(AND(A827=A826,A827&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13958,7 +13968,7 @@
         <v>156</v>
       </c>
       <c r="E828" t="str">
-        <f>IF(AND(A828=A827,A828&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13968,7 +13978,7 @@
         <v>156</v>
       </c>
       <c r="E829" t="str">
-        <f>IF(AND(A829=A828,A829&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13978,7 +13988,7 @@
         <v>156</v>
       </c>
       <c r="E830" t="str">
-        <f>IF(AND(A830=A829,A830&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13988,7 +13998,7 @@
         <v>156</v>
       </c>
       <c r="E831" t="str">
-        <f>IF(AND(A831=A830,A831&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -13998,7 +14008,7 @@
         <v>156</v>
       </c>
       <c r="E832" t="str">
-        <f>IF(AND(A832=A831,A832&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -14008,7 +14018,7 @@
         <v>156</v>
       </c>
       <c r="E833" t="str">
-        <f>IF(AND(A833=A832,A833&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -14018,7 +14028,7 @@
         <v>156</v>
       </c>
       <c r="E834" t="str">
-        <f>IF(AND(A834=A833,A834&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -14028,7 +14038,7 @@
         <v>156</v>
       </c>
       <c r="E835" t="str">
-        <f>IF(AND(A835=A834,A835&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -14038,7 +14048,7 @@
         <v>156</v>
       </c>
       <c r="E836" t="str">
-        <f>IF(AND(A836=A835,A836&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -14048,7 +14058,7 @@
         <v>156</v>
       </c>
       <c r="E837" t="str">
-        <f>IF(AND(A837=A836,A837&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -14058,7 +14068,7 @@
         <v>156</v>
       </c>
       <c r="E838" t="str">
-        <f>IF(AND(A838=A837,A838&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -14068,7 +14078,7 @@
         <v>156</v>
       </c>
       <c r="E839" t="str">
-        <f>IF(AND(A839=A838,A839&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -14078,7 +14088,7 @@
         <v>156</v>
       </c>
       <c r="E840" t="str">
-        <f>IF(AND(A840=A839,A840&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -14088,7 +14098,7 @@
         <v>156</v>
       </c>
       <c r="E841" t="str">
-        <f>IF(AND(A841=A840,A841&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -14098,7 +14108,7 @@
         <v>156</v>
       </c>
       <c r="E842" t="str">
-        <f>IF(AND(A842=A841,A842&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -14108,7 +14118,7 @@
         <v>156</v>
       </c>
       <c r="E843" t="str">
-        <f>IF(AND(A843=A842,A843&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -14118,7 +14128,7 @@
         <v>156</v>
       </c>
       <c r="E844" t="str">
-        <f>IF(AND(A844=A843,A844&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -14128,7 +14138,7 @@
         <v>156</v>
       </c>
       <c r="E845" t="str">
-        <f>IF(AND(A845=A844,A845&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -14138,7 +14148,7 @@
         <v>156</v>
       </c>
       <c r="E846" t="str">
-        <f>IF(AND(A846=A845,A846&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -14148,7 +14158,7 @@
         <v>156</v>
       </c>
       <c r="E847" t="str">
-        <f>IF(AND(A847=A846,A847&lt;&gt;""),1,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -14158,7 +14168,7 @@
         <v>156</v>
       </c>
       <c r="E848" t="str">
-        <f>IF(AND(A848=A847,A848&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E848:E911" si="19">IF(AND(A848=A847,A848&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -14168,7 +14178,7 @@
         <v>156</v>
       </c>
       <c r="E849" t="str">
-        <f>IF(AND(A849=A848,A849&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14178,7 +14188,7 @@
         <v>156</v>
       </c>
       <c r="E850" t="str">
-        <f>IF(AND(A850=A849,A850&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14188,7 +14198,7 @@
         <v>156</v>
       </c>
       <c r="E851" t="str">
-        <f>IF(AND(A851=A850,A851&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14198,7 +14208,7 @@
         <v>156</v>
       </c>
       <c r="E852" t="str">
-        <f>IF(AND(A852=A851,A852&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14208,7 +14218,7 @@
         <v>156</v>
       </c>
       <c r="E853" t="str">
-        <f>IF(AND(A853=A852,A853&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14218,7 +14228,7 @@
         <v>156</v>
       </c>
       <c r="E854" t="str">
-        <f>IF(AND(A854=A853,A854&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14228,7 +14238,7 @@
         <v>156</v>
       </c>
       <c r="E855" t="str">
-        <f>IF(AND(A855=A854,A855&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14238,7 +14248,7 @@
         <v>156</v>
       </c>
       <c r="E856" t="str">
-        <f>IF(AND(A856=A855,A856&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14248,7 +14258,7 @@
         <v>156</v>
       </c>
       <c r="E857" t="str">
-        <f>IF(AND(A857=A856,A857&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14258,7 +14268,7 @@
         <v>156</v>
       </c>
       <c r="E858" t="str">
-        <f>IF(AND(A858=A857,A858&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14268,7 +14278,7 @@
         <v>156</v>
       </c>
       <c r="E859" t="str">
-        <f>IF(AND(A859=A858,A859&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14278,7 +14288,7 @@
         <v>156</v>
       </c>
       <c r="E860" t="str">
-        <f>IF(AND(A860=A859,A860&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14288,7 +14298,7 @@
         <v>156</v>
       </c>
       <c r="E861" t="str">
-        <f>IF(AND(A861=A860,A861&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14298,7 +14308,7 @@
         <v>156</v>
       </c>
       <c r="E862" t="str">
-        <f>IF(AND(A862=A861,A862&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14308,7 +14318,7 @@
         <v>156</v>
       </c>
       <c r="E863" t="str">
-        <f>IF(AND(A863=A862,A863&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14318,7 +14328,7 @@
         <v>156</v>
       </c>
       <c r="E864" t="str">
-        <f>IF(AND(A864=A863,A864&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14328,7 +14338,7 @@
         <v>156</v>
       </c>
       <c r="E865" t="str">
-        <f>IF(AND(A865=A864,A865&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14338,7 +14348,7 @@
         <v>156</v>
       </c>
       <c r="E866" t="str">
-        <f>IF(AND(A866=A865,A866&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14348,7 +14358,7 @@
         <v>156</v>
       </c>
       <c r="E867" t="str">
-        <f>IF(AND(A867=A866,A867&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14358,7 +14368,7 @@
         <v>156</v>
       </c>
       <c r="E868" t="str">
-        <f>IF(AND(A868=A867,A868&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14368,7 +14378,7 @@
         <v>156</v>
       </c>
       <c r="E869" t="str">
-        <f>IF(AND(A869=A868,A869&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14378,7 +14388,7 @@
         <v>156</v>
       </c>
       <c r="E870" t="str">
-        <f>IF(AND(A870=A869,A870&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14388,7 +14398,7 @@
         <v>156</v>
       </c>
       <c r="E871" t="str">
-        <f>IF(AND(A871=A870,A871&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14398,7 +14408,7 @@
         <v>156</v>
       </c>
       <c r="E872" t="str">
-        <f>IF(AND(A872=A871,A872&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14408,7 +14418,7 @@
         <v>156</v>
       </c>
       <c r="E873" t="str">
-        <f>IF(AND(A873=A872,A873&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14418,7 +14428,7 @@
         <v>156</v>
       </c>
       <c r="E874" t="str">
-        <f>IF(AND(A874=A873,A874&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14428,7 +14438,7 @@
         <v>156</v>
       </c>
       <c r="E875" t="str">
-        <f>IF(AND(A875=A874,A875&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14438,7 +14448,7 @@
         <v>156</v>
       </c>
       <c r="E876" t="str">
-        <f>IF(AND(A876=A875,A876&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14448,7 +14458,7 @@
         <v>156</v>
       </c>
       <c r="E877" t="str">
-        <f>IF(AND(A877=A876,A877&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14458,7 +14468,7 @@
         <v>156</v>
       </c>
       <c r="E878" t="str">
-        <f>IF(AND(A878=A877,A878&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14468,7 +14478,7 @@
         <v>156</v>
       </c>
       <c r="E879" t="str">
-        <f>IF(AND(A879=A878,A879&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14478,7 +14488,7 @@
         <v>156</v>
       </c>
       <c r="E880" t="str">
-        <f>IF(AND(A880=A879,A880&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14488,7 +14498,7 @@
         <v>156</v>
       </c>
       <c r="E881" t="str">
-        <f>IF(AND(A881=A880,A881&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14498,7 +14508,7 @@
         <v>156</v>
       </c>
       <c r="E882" t="str">
-        <f>IF(AND(A882=A881,A882&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14508,7 +14518,7 @@
         <v>156</v>
       </c>
       <c r="E883" t="str">
-        <f>IF(AND(A883=A882,A883&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14518,7 +14528,7 @@
         <v>156</v>
       </c>
       <c r="E884" t="str">
-        <f>IF(AND(A884=A883,A884&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14528,7 +14538,7 @@
         <v>156</v>
       </c>
       <c r="E885" t="str">
-        <f>IF(AND(A885=A884,A885&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14538,7 +14548,7 @@
         <v>156</v>
       </c>
       <c r="E886" t="str">
-        <f>IF(AND(A886=A885,A886&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14548,7 +14558,7 @@
         <v>156</v>
       </c>
       <c r="E887" t="str">
-        <f>IF(AND(A887=A886,A887&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14558,7 +14568,7 @@
         <v>156</v>
       </c>
       <c r="E888" t="str">
-        <f>IF(AND(A888=A887,A888&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14568,7 +14578,7 @@
         <v>156</v>
       </c>
       <c r="E889" t="str">
-        <f>IF(AND(A889=A888,A889&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14578,7 +14588,7 @@
         <v>156</v>
       </c>
       <c r="E890" t="str">
-        <f>IF(AND(A890=A889,A890&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14588,7 +14598,7 @@
         <v>156</v>
       </c>
       <c r="E891" t="str">
-        <f>IF(AND(A891=A890,A891&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14598,7 +14608,7 @@
         <v>156</v>
       </c>
       <c r="E892" t="str">
-        <f>IF(AND(A892=A891,A892&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14608,7 +14618,7 @@
         <v>156</v>
       </c>
       <c r="E893" t="str">
-        <f>IF(AND(A893=A892,A893&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14618,7 +14628,7 @@
         <v>156</v>
       </c>
       <c r="E894" t="str">
-        <f>IF(AND(A894=A893,A894&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14628,7 +14638,7 @@
         <v>156</v>
       </c>
       <c r="E895" t="str">
-        <f>IF(AND(A895=A894,A895&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14638,7 +14648,7 @@
         <v>156</v>
       </c>
       <c r="E896" t="str">
-        <f>IF(AND(A896=A895,A896&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14648,7 +14658,7 @@
         <v>156</v>
       </c>
       <c r="E897" t="str">
-        <f>IF(AND(A897=A896,A897&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14658,7 +14668,7 @@
         <v>156</v>
       </c>
       <c r="E898" t="str">
-        <f>IF(AND(A898=A897,A898&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14668,7 +14678,7 @@
         <v>156</v>
       </c>
       <c r="E899" t="str">
-        <f>IF(AND(A899=A898,A899&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14678,7 +14688,7 @@
         <v>156</v>
       </c>
       <c r="E900" t="str">
-        <f>IF(AND(A900=A899,A900&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14688,7 +14698,7 @@
         <v>156</v>
       </c>
       <c r="E901" t="str">
-        <f>IF(AND(A901=A900,A901&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14698,7 +14708,7 @@
         <v>156</v>
       </c>
       <c r="E902" t="str">
-        <f>IF(AND(A902=A901,A902&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14708,7 +14718,7 @@
         <v>156</v>
       </c>
       <c r="E903" t="str">
-        <f>IF(AND(A903=A902,A903&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14718,7 +14728,7 @@
         <v>156</v>
       </c>
       <c r="E904" t="str">
-        <f>IF(AND(A904=A903,A904&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14728,7 +14738,7 @@
         <v>156</v>
       </c>
       <c r="E905" t="str">
-        <f>IF(AND(A905=A904,A905&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14738,7 +14748,7 @@
         <v>156</v>
       </c>
       <c r="E906" t="str">
-        <f>IF(AND(A906=A905,A906&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14748,7 +14758,7 @@
         <v>156</v>
       </c>
       <c r="E907" t="str">
-        <f>IF(AND(A907=A906,A907&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14758,7 +14768,7 @@
         <v>156</v>
       </c>
       <c r="E908" t="str">
-        <f>IF(AND(A908=A907,A908&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14768,7 +14778,7 @@
         <v>156</v>
       </c>
       <c r="E909" t="str">
-        <f>IF(AND(A909=A908,A909&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14778,7 +14788,7 @@
         <v>156</v>
       </c>
       <c r="E910" t="str">
-        <f>IF(AND(A910=A909,A910&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14788,7 +14798,7 @@
         <v>156</v>
       </c>
       <c r="E911" t="str">
-        <f>IF(AND(A911=A910,A911&lt;&gt;""),1,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -14798,7 +14808,7 @@
         <v>156</v>
       </c>
       <c r="E912" t="str">
-        <f>IF(AND(A912=A911,A912&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E912:E975" si="20">IF(AND(A912=A911,A912&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -14808,7 +14818,7 @@
         <v>156</v>
       </c>
       <c r="E913" t="str">
-        <f>IF(AND(A913=A912,A913&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14818,7 +14828,7 @@
         <v>156</v>
       </c>
       <c r="E914" t="str">
-        <f>IF(AND(A914=A913,A914&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14828,7 +14838,7 @@
         <v>156</v>
       </c>
       <c r="E915" t="str">
-        <f>IF(AND(A915=A914,A915&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14838,7 +14848,7 @@
         <v>156</v>
       </c>
       <c r="E916" t="str">
-        <f>IF(AND(A916=A915,A916&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14848,7 +14858,7 @@
         <v>156</v>
       </c>
       <c r="E917" t="str">
-        <f>IF(AND(A917=A916,A917&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14858,7 +14868,7 @@
         <v>156</v>
       </c>
       <c r="E918" t="str">
-        <f>IF(AND(A918=A917,A918&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14868,7 +14878,7 @@
         <v>156</v>
       </c>
       <c r="E919" t="str">
-        <f>IF(AND(A919=A918,A919&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14878,7 +14888,7 @@
         <v>156</v>
       </c>
       <c r="E920" t="str">
-        <f>IF(AND(A920=A919,A920&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14888,7 +14898,7 @@
         <v>156</v>
       </c>
       <c r="E921" t="str">
-        <f>IF(AND(A921=A920,A921&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14898,7 +14908,7 @@
         <v>156</v>
       </c>
       <c r="E922" t="str">
-        <f>IF(AND(A922=A921,A922&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14908,7 +14918,7 @@
         <v>156</v>
       </c>
       <c r="E923" t="str">
-        <f>IF(AND(A923=A922,A923&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14918,7 +14928,7 @@
         <v>156</v>
       </c>
       <c r="E924" t="str">
-        <f>IF(AND(A924=A923,A924&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14928,7 +14938,7 @@
         <v>156</v>
       </c>
       <c r="E925" t="str">
-        <f>IF(AND(A925=A924,A925&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14938,7 +14948,7 @@
         <v>156</v>
       </c>
       <c r="E926" t="str">
-        <f>IF(AND(A926=A925,A926&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14948,7 +14958,7 @@
         <v>156</v>
       </c>
       <c r="E927" t="str">
-        <f>IF(AND(A927=A926,A927&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14958,7 +14968,7 @@
         <v>156</v>
       </c>
       <c r="E928" t="str">
-        <f>IF(AND(A928=A927,A928&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14968,7 +14978,7 @@
         <v>156</v>
       </c>
       <c r="E929" t="str">
-        <f>IF(AND(A929=A928,A929&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14978,7 +14988,7 @@
         <v>156</v>
       </c>
       <c r="E930" t="str">
-        <f>IF(AND(A930=A929,A930&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14988,7 +14998,7 @@
         <v>156</v>
       </c>
       <c r="E931" t="str">
-        <f>IF(AND(A931=A930,A931&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -14998,7 +15008,7 @@
         <v>156</v>
       </c>
       <c r="E932" t="str">
-        <f>IF(AND(A932=A931,A932&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15008,7 +15018,7 @@
         <v>156</v>
       </c>
       <c r="E933" t="str">
-        <f>IF(AND(A933=A932,A933&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15018,7 +15028,7 @@
         <v>156</v>
       </c>
       <c r="E934" t="str">
-        <f>IF(AND(A934=A933,A934&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15028,7 +15038,7 @@
         <v>156</v>
       </c>
       <c r="E935" t="str">
-        <f>IF(AND(A935=A934,A935&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15038,7 +15048,7 @@
         <v>156</v>
       </c>
       <c r="E936" t="str">
-        <f>IF(AND(A936=A935,A936&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15048,7 +15058,7 @@
         <v>156</v>
       </c>
       <c r="E937" t="str">
-        <f>IF(AND(A937=A936,A937&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15058,7 +15068,7 @@
         <v>156</v>
       </c>
       <c r="E938" t="str">
-        <f>IF(AND(A938=A937,A938&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15068,7 +15078,7 @@
         <v>156</v>
       </c>
       <c r="E939" t="str">
-        <f>IF(AND(A939=A938,A939&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15078,7 +15088,7 @@
         <v>156</v>
       </c>
       <c r="E940" t="str">
-        <f>IF(AND(A940=A939,A940&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15088,7 +15098,7 @@
         <v>156</v>
       </c>
       <c r="E941" t="str">
-        <f>IF(AND(A941=A940,A941&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15098,7 +15108,7 @@
         <v>156</v>
       </c>
       <c r="E942" t="str">
-        <f>IF(AND(A942=A941,A942&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15108,7 +15118,7 @@
         <v>156</v>
       </c>
       <c r="E943" t="str">
-        <f>IF(AND(A943=A942,A943&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15118,7 +15128,7 @@
         <v>156</v>
       </c>
       <c r="E944" t="str">
-        <f>IF(AND(A944=A943,A944&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15128,7 +15138,7 @@
         <v>156</v>
       </c>
       <c r="E945" t="str">
-        <f>IF(AND(A945=A944,A945&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15138,7 +15148,7 @@
         <v>156</v>
       </c>
       <c r="E946" t="str">
-        <f>IF(AND(A946=A945,A946&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15148,7 +15158,7 @@
         <v>156</v>
       </c>
       <c r="E947" t="str">
-        <f>IF(AND(A947=A946,A947&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15158,7 +15168,7 @@
         <v>156</v>
       </c>
       <c r="E948" t="str">
-        <f>IF(AND(A948=A947,A948&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15168,7 +15178,7 @@
         <v>156</v>
       </c>
       <c r="E949" t="str">
-        <f>IF(AND(A949=A948,A949&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15178,7 +15188,7 @@
         <v>156</v>
       </c>
       <c r="E950" t="str">
-        <f>IF(AND(A950=A949,A950&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15188,7 +15198,7 @@
         <v>156</v>
       </c>
       <c r="E951" t="str">
-        <f>IF(AND(A951=A950,A951&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15198,7 +15208,7 @@
         <v>156</v>
       </c>
       <c r="E952" t="str">
-        <f>IF(AND(A952=A951,A952&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15208,7 +15218,7 @@
         <v>156</v>
       </c>
       <c r="E953" t="str">
-        <f>IF(AND(A953=A952,A953&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15218,7 +15228,7 @@
         <v>156</v>
       </c>
       <c r="E954" t="str">
-        <f>IF(AND(A954=A953,A954&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15228,7 +15238,7 @@
         <v>156</v>
       </c>
       <c r="E955" t="str">
-        <f>IF(AND(A955=A954,A955&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15238,7 +15248,7 @@
         <v>156</v>
       </c>
       <c r="E956" t="str">
-        <f>IF(AND(A956=A955,A956&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15248,7 +15258,7 @@
         <v>156</v>
       </c>
       <c r="E957" t="str">
-        <f>IF(AND(A957=A956,A957&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15258,7 +15268,7 @@
         <v>156</v>
       </c>
       <c r="E958" t="str">
-        <f>IF(AND(A958=A957,A958&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15268,7 +15278,7 @@
         <v>156</v>
       </c>
       <c r="E959" t="str">
-        <f>IF(AND(A959=A958,A959&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15278,7 +15288,7 @@
         <v>156</v>
       </c>
       <c r="E960" t="str">
-        <f>IF(AND(A960=A959,A960&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15288,7 +15298,7 @@
         <v>156</v>
       </c>
       <c r="E961" t="str">
-        <f>IF(AND(A961=A960,A961&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15298,7 +15308,7 @@
         <v>156</v>
       </c>
       <c r="E962" t="str">
-        <f>IF(AND(A962=A961,A962&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15308,7 +15318,7 @@
         <v>156</v>
       </c>
       <c r="E963" t="str">
-        <f>IF(AND(A963=A962,A963&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15318,7 +15328,7 @@
         <v>156</v>
       </c>
       <c r="E964" t="str">
-        <f>IF(AND(A964=A963,A964&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15328,7 +15338,7 @@
         <v>156</v>
       </c>
       <c r="E965" t="str">
-        <f>IF(AND(A965=A964,A965&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15338,7 +15348,7 @@
         <v>156</v>
       </c>
       <c r="E966" t="str">
-        <f>IF(AND(A966=A965,A966&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15348,7 +15358,7 @@
         <v>156</v>
       </c>
       <c r="E967" t="str">
-        <f>IF(AND(A967=A966,A967&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15358,7 +15368,7 @@
         <v>156</v>
       </c>
       <c r="E968" t="str">
-        <f>IF(AND(A968=A967,A968&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15368,7 +15378,7 @@
         <v>156</v>
       </c>
       <c r="E969" t="str">
-        <f>IF(AND(A969=A968,A969&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15378,7 +15388,7 @@
         <v>156</v>
       </c>
       <c r="E970" t="str">
-        <f>IF(AND(A970=A969,A970&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15388,7 +15398,7 @@
         <v>156</v>
       </c>
       <c r="E971" t="str">
-        <f>IF(AND(A971=A970,A971&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15398,7 +15408,7 @@
         <v>156</v>
       </c>
       <c r="E972" t="str">
-        <f>IF(AND(A972=A971,A972&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15408,7 +15418,7 @@
         <v>156</v>
       </c>
       <c r="E973" t="str">
-        <f>IF(AND(A973=A972,A973&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15418,7 +15428,7 @@
         <v>156</v>
       </c>
       <c r="E974" t="str">
-        <f>IF(AND(A974=A973,A974&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15428,7 +15438,7 @@
         <v>156</v>
       </c>
       <c r="E975" t="str">
-        <f>IF(AND(A975=A974,A975&lt;&gt;""),1,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -15438,7 +15448,7 @@
         <v>156</v>
       </c>
       <c r="E976" t="str">
-        <f>IF(AND(A976=A975,A976&lt;&gt;""),1,"")</f>
+        <f t="shared" ref="E976:E994" si="21">IF(AND(A976=A975,A976&lt;&gt;""),1,"")</f>
         <v/>
       </c>
     </row>
@@ -15448,7 +15458,7 @@
         <v>156</v>
       </c>
       <c r="E977" t="str">
-        <f>IF(AND(A977=A976,A977&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15458,7 +15468,7 @@
         <v>156</v>
       </c>
       <c r="E978" t="str">
-        <f>IF(AND(A978=A977,A978&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15468,7 +15478,7 @@
         <v>156</v>
       </c>
       <c r="E979" t="str">
-        <f>IF(AND(A979=A978,A979&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15478,7 +15488,7 @@
         <v>156</v>
       </c>
       <c r="E980" t="str">
-        <f>IF(AND(A980=A979,A980&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15488,7 +15498,7 @@
         <v>156</v>
       </c>
       <c r="E981" t="str">
-        <f>IF(AND(A981=A980,A981&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15498,7 +15508,7 @@
         <v>156</v>
       </c>
       <c r="E982" t="str">
-        <f>IF(AND(A982=A981,A982&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15508,7 +15518,7 @@
         <v>156</v>
       </c>
       <c r="E983" t="str">
-        <f>IF(AND(A983=A982,A983&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15518,7 +15528,7 @@
         <v>156</v>
       </c>
       <c r="E984" t="str">
-        <f>IF(AND(A984=A983,A984&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15528,7 +15538,7 @@
         <v>156</v>
       </c>
       <c r="E985" t="str">
-        <f>IF(AND(A985=A984,A985&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15538,7 +15548,7 @@
         <v>156</v>
       </c>
       <c r="E986" t="str">
-        <f>IF(AND(A986=A985,A986&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15548,7 +15558,7 @@
         <v>156</v>
       </c>
       <c r="E987" t="str">
-        <f>IF(AND(A987=A986,A987&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15558,7 +15568,7 @@
         <v>156</v>
       </c>
       <c r="E988" t="str">
-        <f>IF(AND(A988=A987,A988&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15568,7 +15578,7 @@
         <v>156</v>
       </c>
       <c r="E989" t="str">
-        <f>IF(AND(A989=A988,A989&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15578,7 +15588,7 @@
         <v>156</v>
       </c>
       <c r="E990" t="str">
-        <f>IF(AND(A990=A989,A990&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15588,7 +15598,7 @@
         <v>156</v>
       </c>
       <c r="E991" t="str">
-        <f>IF(AND(A991=A990,A991&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15598,7 +15608,7 @@
         <v>156</v>
       </c>
       <c r="E992" t="str">
-        <f>IF(AND(A992=A991,A992&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15608,7 +15618,7 @@
         <v>156</v>
       </c>
       <c r="E993" t="str">
-        <f>IF(AND(A993=A992,A993&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -15618,7 +15628,7 @@
         <v>156</v>
       </c>
       <c r="E994" t="str">
-        <f>IF(AND(A994=A993,A994&lt;&gt;""),1,"")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>

--- a/Mng/Acronyms.xlsx
+++ b/Mng/Acronyms.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D4AB3A-6499-4EF5-A742-D418C8015072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C912A69D-99BE-47FE-9E96-271DF7B7A24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294947668" uniqueCount="856">
   <si>
     <t>GW</t>
   </si>
@@ -1573,9 +1573,6 @@
     <t>Statistics</t>
   </si>
   <si>
-    <t>l</t>
-  </si>
-  <si>
     <t>list</t>
   </si>
   <si>
@@ -2877,6 +2874,9 @@
   </si>
   <si>
     <t>Decline</t>
+  </si>
+  <si>
+    <t>l_</t>
   </si>
 </sst>
 </file>
@@ -3448,7 +3448,7 @@
         <v>155</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>81</v>
@@ -3473,15 +3473,15 @@
       </c>
       <c r="F2" s="4">
         <f>SUM(E2:E994)</f>
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>292</v>
@@ -3493,13 +3493,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>756</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>757</v>
-      </c>
       <c r="C4" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
@@ -3508,13 +3508,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>641</v>
-      </c>
       <c r="C5" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>58</v>
@@ -3727,10 +3727,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>300</v>
@@ -3757,16 +3757,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>300</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
@@ -3791,16 +3791,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>787</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>788</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>300</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E23" t="str">
         <f t="shared" si="0"/>
@@ -3824,7 +3824,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>51</v>
@@ -3843,7 +3843,7 @@
         <v>356</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>290</v>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>842</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>843</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>292</v>
@@ -3886,10 +3886,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>608</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>609</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>292</v>
@@ -3901,10 +3901,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>794</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>795</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>292</v>
@@ -3931,10 +3931,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>752</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>753</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>292</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>750</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>751</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>300</v>
@@ -3977,13 +3977,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>770</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>771</v>
-      </c>
       <c r="C35" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E35" t="str">
         <f t="shared" si="1"/>
@@ -3992,10 +3992,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>627</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>628</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>300</v>
@@ -4007,13 +4007,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
+        <v>545</v>
+      </c>
+      <c r="B37" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="B37" s="11" t="s">
-        <v>547</v>
-      </c>
       <c r="C37" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E37" t="str">
         <f t="shared" si="1"/>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>498</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>499</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>292</v>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>703</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>704</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>300</v>
@@ -4098,10 +4098,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>673</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>674</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>292</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>701</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>702</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>300</v>
@@ -4128,10 +4128,10 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>292</v>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>300</v>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>817</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>818</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>300</v>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>300</v>
@@ -4188,10 +4188,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>743</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>744</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>300</v>
@@ -4203,10 +4203,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>462</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>463</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>292</v>
@@ -4218,13 +4218,13 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="B51" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>805</v>
-      </c>
       <c r="C51" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E51" t="str">
         <f t="shared" si="1"/>
@@ -4233,10 +4233,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>688</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>689</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>292</v>
@@ -4267,10 +4267,10 @@
         <v>275</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E54">
         <f t="shared" si="1"/>
@@ -4282,7 +4282,7 @@
         <v>275</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>293</v>
@@ -4294,10 +4294,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>819</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>820</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>300</v>
@@ -4345,10 +4345,10 @@
         <v>260</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E59">
         <f t="shared" si="1"/>
@@ -4357,10 +4357,10 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
+        <v>595</v>
+      </c>
+      <c r="B60" s="12" t="s">
         <v>596</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>597</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>292</v>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="B61" s="5" t="s">
         <v>854</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>855</v>
       </c>
       <c r="E61" t="str">
         <f t="shared" si="1"/>
@@ -4384,10 +4384,10 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>636</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>637</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>300</v>
@@ -4414,13 +4414,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>432</v>
-      </c>
       <c r="C64" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E64" t="str">
         <f t="shared" si="1"/>
@@ -4429,10 +4429,10 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>453</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>454</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>182</v>
@@ -4460,10 +4460,10 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="B67" s="5" t="s">
         <v>662</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>663</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>300</v>
@@ -4490,13 +4490,13 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="B69" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="B69" s="5" t="s">
-        <v>443</v>
-      </c>
       <c r="C69" s="5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E69" t="str">
         <f t="shared" si="2"/>
@@ -4520,13 +4520,13 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
+        <v>565</v>
+      </c>
+      <c r="B71" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="B71" s="11" t="s">
-        <v>567</v>
-      </c>
       <c r="C71" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E71">
         <f t="shared" si="2"/>
@@ -4535,10 +4535,10 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B72" s="5" t="s">
         <v>796</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>797</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>300</v>
@@ -4550,13 +4550,13 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
+        <v>569</v>
+      </c>
+      <c r="B73" s="11" t="s">
         <v>570</v>
       </c>
-      <c r="B73" s="11" t="s">
-        <v>571</v>
-      </c>
       <c r="C73" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E73" t="str">
         <f t="shared" si="2"/>
@@ -4565,13 +4565,13 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="B74" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="B74" s="11" t="s">
-        <v>569</v>
-      </c>
       <c r="C74" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E74" t="str">
         <f t="shared" si="2"/>
@@ -4580,10 +4580,10 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>300</v>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>292</v>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
+        <v>549</v>
+      </c>
+      <c r="B80" s="11" t="s">
         <v>550</v>
       </c>
-      <c r="B80" s="11" t="s">
-        <v>551</v>
-      </c>
       <c r="C80" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E80">
         <f t="shared" si="2"/>
@@ -4685,10 +4685,10 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>292</v>
@@ -4700,10 +4700,10 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="B83" s="5" t="s">
         <v>745</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>746</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>292</v>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="B84" s="5" t="s">
         <v>504</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>505</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>300</v>
@@ -4872,10 +4872,10 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>292</v>
@@ -4917,10 +4917,10 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="B97" s="5" t="s">
         <v>714</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>715</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>300</v>
@@ -4948,10 +4948,10 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="B99" s="5" t="s">
         <v>621</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>622</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>300</v>
@@ -4993,10 +4993,10 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="B102" s="5" t="s">
         <v>492</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>493</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>300</v>
@@ -5008,13 +5008,13 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E103">
         <f t="shared" si="3"/>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="B104" s="5" t="s">
         <v>831</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>832</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>300</v>
@@ -5038,10 +5038,10 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="B105" s="5" t="s">
         <v>638</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>639</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>292</v>
@@ -5099,10 +5099,10 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>292</v>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="B110" s="5" t="s">
         <v>478</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>479</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>292</v>
@@ -5129,10 +5129,10 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="B111" s="5" t="s">
         <v>538</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>539</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>292</v>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
+        <v>685</v>
+      </c>
+      <c r="B113" s="5" t="s">
         <v>686</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>687</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>300</v>
@@ -5174,10 +5174,10 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="B114" s="5" t="s">
         <v>470</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>471</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>290</v>
@@ -5189,10 +5189,10 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="B115" s="5" t="s">
         <v>707</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>708</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>300</v>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="B116" s="5" t="s">
         <v>718</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>719</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>300</v>
@@ -5219,10 +5219,10 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="B117" s="5" t="s">
         <v>434</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>435</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>292</v>
@@ -5234,13 +5234,13 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="B118" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="B118" s="5" t="s">
+      <c r="C118" s="5" t="s">
         <v>440</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>441</v>
       </c>
       <c r="E118" t="str">
         <f t="shared" si="3"/>
@@ -5312,10 +5312,10 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>777</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>778</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>292</v>
@@ -5327,7 +5327,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>301</v>
@@ -5342,10 +5342,10 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="B125" s="5" t="s">
         <v>468</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>469</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>292</v>
@@ -5357,13 +5357,13 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="B126" s="11" t="s">
         <v>553</v>
       </c>
-      <c r="B126" s="11" t="s">
-        <v>554</v>
-      </c>
       <c r="C126" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E126" t="str">
         <f t="shared" si="3"/>
@@ -5437,13 +5437,13 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="B131" s="11" t="s">
         <v>583</v>
       </c>
-      <c r="B131" s="11" t="s">
-        <v>584</v>
-      </c>
       <c r="C131" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E131" t="str">
         <f t="shared" si="4"/>
@@ -5467,10 +5467,10 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>300</v>
@@ -5482,10 +5482,10 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>292</v>
@@ -5604,10 +5604,10 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="B142" s="5" t="s">
         <v>482</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>483</v>
       </c>
       <c r="C142" s="5" t="s">
         <v>292</v>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B150" s="5" t="s">
         <v>460</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>461</v>
       </c>
       <c r="C150" s="5" t="s">
         <v>292</v>
@@ -5759,7 +5759,7 @@
         <v>311</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C152" s="5" t="s">
         <v>292</v>
@@ -5801,10 +5801,10 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="B155" s="5" t="s">
         <v>611</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>612</v>
       </c>
       <c r="C155" s="5" t="s">
         <v>292</v>
@@ -5816,10 +5816,10 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C156" s="5" t="s">
         <v>300</v>
@@ -5846,10 +5846,10 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="B158" s="5" t="s">
         <v>838</v>
-      </c>
-      <c r="B158" s="5" t="s">
-        <v>839</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>292</v>
@@ -5861,13 +5861,13 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="B159" s="11" t="s">
         <v>575</v>
       </c>
-      <c r="B159" s="11" t="s">
-        <v>576</v>
-      </c>
       <c r="C159" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E159" t="str">
         <f t="shared" si="4"/>
@@ -5876,10 +5876,10 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="B160" s="5" t="s">
         <v>675</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>676</v>
       </c>
       <c r="C160" s="5" t="s">
         <v>300</v>
@@ -5921,13 +5921,13 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="B163" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="B163" s="11" t="s">
-        <v>586</v>
-      </c>
       <c r="C163" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E163" t="str">
         <f t="shared" si="5"/>
@@ -5936,16 +5936,16 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="B164" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="B164" s="5" t="s">
-        <v>525</v>
-      </c>
       <c r="C164" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E164" t="str">
         <f t="shared" si="5"/>
@@ -5969,10 +5969,10 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="B166" s="5" t="s">
         <v>852</v>
-      </c>
-      <c r="B166" s="5" t="s">
-        <v>853</v>
       </c>
       <c r="E166" t="str">
         <f t="shared" si="5"/>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C168" s="5" t="s">
         <v>292</v>
@@ -6011,10 +6011,10 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="B169" s="5" t="s">
         <v>682</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>683</v>
       </c>
       <c r="C169" s="5" t="s">
         <v>300</v>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="B170" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="B170" s="5" t="s">
-        <v>430</v>
-      </c>
       <c r="C170" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E170" t="str">
         <f t="shared" si="5"/>
@@ -6041,10 +6041,10 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C171" s="5" t="s">
         <v>300</v>
@@ -6056,10 +6056,10 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="B172" s="5" t="s">
         <v>496</v>
-      </c>
-      <c r="B172" s="5" t="s">
-        <v>497</v>
       </c>
       <c r="C172" s="5" t="s">
         <v>300</v>
@@ -6086,10 +6086,10 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C174" s="5" t="s">
         <v>292</v>
@@ -6097,10 +6097,10 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="5" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C175" s="5" t="s">
         <v>300</v>
@@ -6112,10 +6112,10 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="B176" s="5" t="s">
         <v>634</v>
-      </c>
-      <c r="B176" s="5" t="s">
-        <v>635</v>
       </c>
       <c r="C176" s="5" t="s">
         <v>292</v>
@@ -6188,7 +6188,7 @@
         <v>296</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E180" t="str">
         <f t="shared" si="6"/>
@@ -6197,17 +6197,17 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="5" t="s">
+        <v>855</v>
+      </c>
+      <c r="B181" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="B181" s="5" t="s">
+      <c r="C181" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="C181" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="E181">
+      <c r="E181" t="str">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
@@ -6215,25 +6215,25 @@
         <v>294</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C182" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="E182">
+      <c r="E182" t="str">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="11" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B183" s="11" t="s">
         <v>173</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E183" t="str">
         <f t="shared" si="6"/>
@@ -6242,10 +6242,10 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="B184" s="5" t="s">
         <v>522</v>
-      </c>
-      <c r="B184" s="5" t="s">
-        <v>523</v>
       </c>
       <c r="C184" s="5" t="s">
         <v>292</v>
@@ -6257,10 +6257,10 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="B185" s="5" t="s">
         <v>480</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>481</v>
       </c>
       <c r="C185" s="5" t="s">
         <v>300</v>
@@ -6287,13 +6287,13 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="B187" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="B187" s="11" t="s">
-        <v>590</v>
-      </c>
       <c r="C187" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E187" t="str">
         <f t="shared" si="6"/>
@@ -6335,10 +6335,10 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="B190" s="5" t="s">
         <v>613</v>
-      </c>
-      <c r="B190" s="5" t="s">
-        <v>614</v>
       </c>
       <c r="C190" s="5" t="s">
         <v>292</v>
@@ -6451,13 +6451,13 @@
         <v>280</v>
       </c>
       <c r="B197" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D197" s="17" t="s">
         <v>850</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="D197" s="17" t="s">
-        <v>851</v>
       </c>
       <c r="E197">
         <f t="shared" si="6"/>
@@ -6466,13 +6466,13 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="B198" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="B198" s="11" t="s">
-        <v>563</v>
-      </c>
       <c r="C198" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E198" t="str">
         <f t="shared" si="6"/>
@@ -6481,10 +6481,10 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="B199" s="5" t="s">
         <v>455</v>
-      </c>
-      <c r="B199" s="5" t="s">
-        <v>456</v>
       </c>
       <c r="C199" s="5" t="s">
         <v>182</v>
@@ -6496,13 +6496,13 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="B200" s="5" t="s">
         <v>691</v>
       </c>
-      <c r="B200" s="5" t="s">
+      <c r="C200" s="5" t="s">
         <v>692</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>693</v>
       </c>
       <c r="E200" t="str">
         <f t="shared" si="6"/>
@@ -6526,10 +6526,10 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="B202" s="5" t="s">
         <v>644</v>
-      </c>
-      <c r="B202" s="5" t="s">
-        <v>645</v>
       </c>
       <c r="C202" s="5" t="s">
         <v>292</v>
@@ -6571,10 +6571,10 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="B205" s="5" t="s">
         <v>781</v>
-      </c>
-      <c r="B205" s="5" t="s">
-        <v>782</v>
       </c>
       <c r="C205" s="5" t="s">
         <v>292</v>
@@ -6586,10 +6586,10 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B206" s="5" t="s">
         <v>457</v>
-      </c>
-      <c r="B206" s="5" t="s">
-        <v>458</v>
       </c>
       <c r="C206" s="5" t="s">
         <v>182</v>
@@ -6601,10 +6601,10 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="B207" s="5" t="s">
         <v>528</v>
-      </c>
-      <c r="B207" s="5" t="s">
-        <v>529</v>
       </c>
       <c r="C207" s="5" t="s">
         <v>292</v>
@@ -6648,10 +6648,10 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="B210" s="5" t="s">
         <v>783</v>
-      </c>
-      <c r="B210" s="5" t="s">
-        <v>784</v>
       </c>
       <c r="C210" s="5" t="s">
         <v>292</v>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="B211" s="5" t="s">
         <v>646</v>
-      </c>
-      <c r="B211" s="5" t="s">
-        <v>647</v>
       </c>
       <c r="C211" s="5" t="s">
         <v>300</v>
@@ -6678,10 +6678,10 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="B212" s="5" t="s">
         <v>630</v>
-      </c>
-      <c r="B212" s="5" t="s">
-        <v>631</v>
       </c>
       <c r="C212" s="5" t="s">
         <v>292</v>
@@ -6693,10 +6693,10 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="B213" s="5" t="s">
         <v>623</v>
-      </c>
-      <c r="B213" s="5" t="s">
-        <v>624</v>
       </c>
       <c r="C213" s="5" t="s">
         <v>182</v>
@@ -6708,13 +6708,13 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="B214" s="11" t="s">
         <v>564</v>
       </c>
-      <c r="B214" s="11" t="s">
-        <v>565</v>
-      </c>
       <c r="C214" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E214" t="str">
         <f t="shared" si="7"/>
@@ -6760,7 +6760,7 @@
         <v>3</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C217" s="5" t="s">
         <v>292</v>
@@ -6837,10 +6837,10 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="B222" s="5" t="s">
         <v>502</v>
-      </c>
-      <c r="B222" s="5" t="s">
-        <v>503</v>
       </c>
       <c r="C222" s="5" t="s">
         <v>300</v>
@@ -6852,10 +6852,10 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="B223" s="5" t="s">
         <v>632</v>
-      </c>
-      <c r="B223" s="5" t="s">
-        <v>633</v>
       </c>
       <c r="C223" s="5" t="s">
         <v>292</v>
@@ -6914,10 +6914,10 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="5" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C227" s="5" t="s">
         <v>300</v>
@@ -6960,10 +6960,10 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="B230" s="5" t="s">
         <v>666</v>
-      </c>
-      <c r="B230" s="5" t="s">
-        <v>667</v>
       </c>
       <c r="C230" s="5" t="s">
         <v>300</v>
@@ -7007,13 +7007,13 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="11" t="s">
+        <v>571</v>
+      </c>
+      <c r="B233" s="11" t="s">
         <v>572</v>
       </c>
-      <c r="B233" s="11" t="s">
-        <v>573</v>
-      </c>
       <c r="C233" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E233" t="str">
         <f t="shared" si="7"/>
@@ -7072,10 +7072,10 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="B237" s="5" t="s">
         <v>800</v>
-      </c>
-      <c r="B237" s="5" t="s">
-        <v>801</v>
       </c>
       <c r="C237" s="5" t="s">
         <v>300</v>
@@ -7087,13 +7087,13 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B238" s="5" t="s">
         <v>766</v>
       </c>
-      <c r="B238" s="5" t="s">
-        <v>767</v>
-      </c>
       <c r="C238" s="5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E238" t="str">
         <f t="shared" si="7"/>
@@ -7133,13 +7133,13 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="B241" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="B241" s="11" t="s">
-        <v>578</v>
-      </c>
       <c r="C241" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E241" t="str">
         <f t="shared" si="7"/>
@@ -7148,10 +7148,10 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C242" s="5" t="s">
         <v>292</v>
@@ -7163,10 +7163,10 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="B243" s="5" t="s">
         <v>657</v>
-      </c>
-      <c r="B243" s="5" t="s">
-        <v>658</v>
       </c>
       <c r="C243" s="5" t="s">
         <v>292</v>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="B246" s="5" t="s">
         <v>668</v>
-      </c>
-      <c r="B246" s="5" t="s">
-        <v>669</v>
       </c>
       <c r="C246" s="5" t="s">
         <v>300</v>
@@ -7223,10 +7223,10 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="B247" s="5" t="s">
         <v>802</v>
-      </c>
-      <c r="B247" s="5" t="s">
-        <v>803</v>
       </c>
       <c r="C247" s="5" t="s">
         <v>300</v>
@@ -7253,10 +7253,10 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="B249" s="5" t="s">
         <v>814</v>
-      </c>
-      <c r="B249" s="5" t="s">
-        <v>815</v>
       </c>
       <c r="C249" s="5" t="s">
         <v>300</v>
@@ -7268,13 +7268,13 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="B250" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="B250" s="5" t="s">
-        <v>527</v>
-      </c>
       <c r="C250" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E250" t="str">
         <f t="shared" si="8"/>
@@ -7326,13 +7326,13 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="B254" s="5" t="s">
         <v>810</v>
       </c>
-      <c r="B254" s="5" t="s">
-        <v>811</v>
-      </c>
       <c r="C254" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E254" t="str">
         <f t="shared" ref="E254:E270" si="9">IF(AND(A254=A253,A254&lt;&gt;""),1,"")</f>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="B255" s="5" t="s">
         <v>710</v>
-      </c>
-      <c r="B255" s="5" t="s">
-        <v>711</v>
       </c>
       <c r="C255" s="5" t="s">
         <v>292</v>
@@ -7356,7 +7356,7 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B256" s="5" t="s">
         <v>299</v>
@@ -7371,10 +7371,10 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="B257" s="5" t="s">
         <v>436</v>
-      </c>
-      <c r="B257" s="5" t="s">
-        <v>437</v>
       </c>
       <c r="C257" s="5" t="s">
         <v>292</v>
@@ -7461,10 +7461,10 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="B263" s="5" t="s">
         <v>680</v>
-      </c>
-      <c r="B263" s="5" t="s">
-        <v>681</v>
       </c>
       <c r="C263" s="5" t="s">
         <v>292</v>
@@ -7476,13 +7476,13 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="B264" s="5" t="s">
         <v>790</v>
       </c>
-      <c r="B264" s="5" t="s">
-        <v>791</v>
-      </c>
       <c r="C264" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E264" t="str">
         <f t="shared" si="9"/>
@@ -7521,10 +7521,10 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="B267" s="5" t="s">
         <v>488</v>
-      </c>
-      <c r="B267" s="5" t="s">
-        <v>489</v>
       </c>
       <c r="C267" s="5" t="s">
         <v>292</v>
@@ -7536,10 +7536,10 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="B268" s="5" t="s">
         <v>653</v>
-      </c>
-      <c r="B268" s="5" t="s">
-        <v>654</v>
       </c>
       <c r="C268" s="5" t="s">
         <v>292</v>
@@ -7567,10 +7567,10 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="B270" s="5" t="s">
         <v>659</v>
-      </c>
-      <c r="B270" s="5" t="s">
-        <v>660</v>
       </c>
       <c r="C270" s="5" t="s">
         <v>292</v>
@@ -7582,7 +7582,7 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B271" s="5" t="s">
         <v>31</v>
@@ -7598,10 +7598,10 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="11" t="s">
+        <v>593</v>
+      </c>
+      <c r="B272" s="12" t="s">
         <v>594</v>
-      </c>
-      <c r="B272" s="12" t="s">
-        <v>595</v>
       </c>
       <c r="C272" s="5" t="s">
         <v>292</v>
@@ -7628,10 +7628,10 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="B274" s="5" t="s">
         <v>542</v>
-      </c>
-      <c r="B274" s="5" t="s">
-        <v>543</v>
       </c>
       <c r="C274" s="5" t="s">
         <v>300</v>
@@ -7659,10 +7659,10 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C276" s="5" t="s">
         <v>292</v>
@@ -7674,10 +7674,10 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="B277" s="5" t="s">
         <v>655</v>
-      </c>
-      <c r="B277" s="5" t="s">
-        <v>656</v>
       </c>
       <c r="C277" s="5" t="s">
         <v>292</v>
@@ -7689,10 +7689,10 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="5" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C278" s="5" t="s">
         <v>292</v>
@@ -7704,10 +7704,10 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="B279" s="5" t="s">
         <v>798</v>
-      </c>
-      <c r="B279" s="5" t="s">
-        <v>799</v>
       </c>
       <c r="C279" s="5" t="s">
         <v>300</v>
@@ -7719,10 +7719,10 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="B280" s="5" t="s">
         <v>740</v>
-      </c>
-      <c r="B280" s="5" t="s">
-        <v>741</v>
       </c>
       <c r="C280" s="5" t="s">
         <v>300</v>
@@ -7734,10 +7734,10 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="B281" s="5" t="s">
         <v>758</v>
-      </c>
-      <c r="B281" s="5" t="s">
-        <v>759</v>
       </c>
       <c r="C281" s="5" t="s">
         <v>300</v>
@@ -7749,10 +7749,10 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="B282" s="5" t="s">
         <v>829</v>
-      </c>
-      <c r="B282" s="5" t="s">
-        <v>830</v>
       </c>
       <c r="C282" s="5" t="s">
         <v>300</v>
@@ -7780,10 +7780,10 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B284" s="5" t="s">
         <v>785</v>
-      </c>
-      <c r="B284" s="5" t="s">
-        <v>786</v>
       </c>
       <c r="C284" s="5" t="s">
         <v>292</v>
@@ -7825,10 +7825,10 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="B287" s="5" t="s">
         <v>606</v>
-      </c>
-      <c r="B287" s="5" t="s">
-        <v>607</v>
       </c>
       <c r="C287" s="5" t="s">
         <v>292</v>
@@ -7840,13 +7840,13 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="B288" s="5" t="s">
         <v>764</v>
       </c>
-      <c r="B288" s="5" t="s">
-        <v>765</v>
-      </c>
       <c r="C288" s="5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E288" t="str">
         <f t="shared" si="10"/>
@@ -7855,10 +7855,10 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="B289" s="5" t="s">
         <v>844</v>
-      </c>
-      <c r="B289" s="5" t="s">
-        <v>845</v>
       </c>
       <c r="C289" s="5" t="s">
         <v>292</v>
@@ -7885,13 +7885,13 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="11" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B291" s="11" t="s">
         <v>378</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E291">
         <f t="shared" si="10"/>
@@ -7900,10 +7900,10 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="B292" s="5" t="s">
         <v>760</v>
-      </c>
-      <c r="B292" s="5" t="s">
-        <v>761</v>
       </c>
       <c r="C292" s="5" t="s">
         <v>300</v>
@@ -7915,10 +7915,10 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="5" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C293" s="5" t="s">
         <v>300</v>
@@ -7945,10 +7945,10 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="B295" s="5" t="s">
         <v>602</v>
-      </c>
-      <c r="B295" s="5" t="s">
-        <v>603</v>
       </c>
       <c r="C295" s="5" t="s">
         <v>300</v>
@@ -7960,10 +7960,10 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="B296" s="5" t="s">
         <v>444</v>
-      </c>
-      <c r="B296" s="5" t="s">
-        <v>445</v>
       </c>
       <c r="C296" s="5" t="s">
         <v>300</v>
@@ -8005,16 +8005,16 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B299" s="5" t="s">
         <v>772</v>
-      </c>
-      <c r="B299" s="5" t="s">
-        <v>773</v>
       </c>
       <c r="C299" s="5" t="s">
         <v>292</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E299" t="str">
         <f t="shared" si="10"/>
@@ -8023,10 +8023,10 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="B300" s="5" t="s">
         <v>705</v>
-      </c>
-      <c r="B300" s="5" t="s">
-        <v>706</v>
       </c>
       <c r="C300" s="5" t="s">
         <v>300</v>
@@ -8038,13 +8038,13 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="11" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B301" s="11" t="s">
         <v>172</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E301" t="str">
         <f t="shared" si="10"/>
@@ -8053,13 +8053,13 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="B302" s="5" t="s">
         <v>670</v>
       </c>
-      <c r="B302" s="5" t="s">
-        <v>671</v>
-      </c>
       <c r="C302" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E302" t="str">
         <f t="shared" si="10"/>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="B303" s="5" t="s">
         <v>840</v>
-      </c>
-      <c r="B303" s="5" t="s">
-        <v>841</v>
       </c>
       <c r="C303" s="5" t="s">
         <v>292</v>
@@ -8083,10 +8083,10 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="5" t="s">
+        <v>715</v>
+      </c>
+      <c r="B304" s="5" t="s">
         <v>716</v>
-      </c>
-      <c r="B304" s="5" t="s">
-        <v>717</v>
       </c>
       <c r="C304" s="5" t="s">
         <v>300</v>
@@ -8113,10 +8113,10 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="B306" s="5" t="s">
         <v>500</v>
-      </c>
-      <c r="B306" s="5" t="s">
-        <v>501</v>
       </c>
       <c r="C306" s="5" t="s">
         <v>292</v>
@@ -8159,13 +8159,13 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="B309" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B309" s="5" t="s">
-        <v>426</v>
-      </c>
       <c r="C309" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E309">
         <f t="shared" si="10"/>
@@ -8183,7 +8183,7 @@
         <v>292</v>
       </c>
       <c r="D310" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E310">
         <f t="shared" si="10"/>
@@ -8192,10 +8192,10 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="B311" s="5" t="s">
         <v>544</v>
-      </c>
-      <c r="B311" s="5" t="s">
-        <v>545</v>
       </c>
       <c r="C311" s="5" t="s">
         <v>292</v>
@@ -8238,10 +8238,10 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="B314" s="5" t="s">
         <v>734</v>
-      </c>
-      <c r="B314" s="5" t="s">
-        <v>735</v>
       </c>
       <c r="C314" s="5" t="s">
         <v>300</v>
@@ -8253,10 +8253,10 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" s="5" t="s">
+        <v>731</v>
+      </c>
+      <c r="B315" s="5" t="s">
         <v>732</v>
-      </c>
-      <c r="B315" s="5" t="s">
-        <v>733</v>
       </c>
       <c r="C315" s="5" t="s">
         <v>292</v>
@@ -8299,13 +8299,13 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="5" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D318" s="5"/>
       <c r="E318" t="str">
@@ -8347,13 +8347,13 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="B321" s="5" t="s">
         <v>848</v>
       </c>
-      <c r="B321" s="5" t="s">
-        <v>849</v>
-      </c>
       <c r="C321" s="5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E321" t="str">
         <f t="shared" si="10"/>
@@ -8378,13 +8378,13 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="B323" s="11" t="s">
         <v>555</v>
       </c>
-      <c r="B323" s="11" t="s">
-        <v>556</v>
-      </c>
       <c r="C323" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E323" t="str">
         <f t="shared" si="10"/>
@@ -8393,13 +8393,13 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="B324" s="11" t="s">
         <v>587</v>
       </c>
-      <c r="B324" s="11" t="s">
-        <v>588</v>
-      </c>
       <c r="C324" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E324" t="str">
         <f t="shared" si="10"/>
@@ -8408,10 +8408,10 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="B325" s="5" t="s">
         <v>518</v>
-      </c>
-      <c r="B325" s="5" t="s">
-        <v>519</v>
       </c>
       <c r="C325" s="5" t="s">
         <v>292</v>
@@ -8423,10 +8423,10 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="B326" s="5" t="s">
         <v>808</v>
-      </c>
-      <c r="B326" s="5" t="s">
-        <v>809</v>
       </c>
       <c r="C326" s="5" t="s">
         <v>300</v>
@@ -8453,10 +8453,10 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="B328" s="5" t="s">
         <v>825</v>
-      </c>
-      <c r="B328" s="5" t="s">
-        <v>826</v>
       </c>
       <c r="C328" s="5" t="s">
         <v>292</v>
@@ -8468,10 +8468,10 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="B329" s="5" t="s">
         <v>724</v>
-      </c>
-      <c r="B329" s="5" t="s">
-        <v>725</v>
       </c>
       <c r="C329" s="5" t="s">
         <v>300</v>
@@ -8499,10 +8499,10 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B331" s="5" t="s">
         <v>506</v>
-      </c>
-      <c r="B331" s="5" t="s">
-        <v>507</v>
       </c>
       <c r="C331" s="5" t="s">
         <v>292</v>
@@ -8514,10 +8514,10 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="B332" s="5" t="s">
         <v>532</v>
-      </c>
-      <c r="B332" s="5" t="s">
-        <v>533</v>
       </c>
       <c r="C332" s="5" t="s">
         <v>292</v>
@@ -8560,10 +8560,10 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="B335" s="5" t="s">
         <v>510</v>
-      </c>
-      <c r="B335" s="5" t="s">
-        <v>511</v>
       </c>
       <c r="C335" s="5" t="s">
         <v>292</v>
@@ -8575,10 +8575,10 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="B336" s="5" t="s">
         <v>512</v>
-      </c>
-      <c r="B336" s="5" t="s">
-        <v>513</v>
       </c>
       <c r="C336" s="5" t="s">
         <v>292</v>
@@ -8590,13 +8590,13 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="5" t="s">
+        <v>721</v>
+      </c>
+      <c r="B337" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="B337" s="5" t="s">
-        <v>723</v>
-      </c>
       <c r="C337" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E337" t="str">
         <f t="shared" si="11"/>
@@ -8621,13 +8621,13 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" s="11" t="s">
+        <v>578</v>
+      </c>
+      <c r="B339" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="B339" s="11" t="s">
-        <v>580</v>
-      </c>
       <c r="C339" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E339" t="str">
         <f t="shared" si="11"/>
@@ -8667,10 +8667,10 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="B342" s="5" t="s">
         <v>520</v>
-      </c>
-      <c r="B342" s="5" t="s">
-        <v>521</v>
       </c>
       <c r="C342" s="5" t="s">
         <v>292</v>
@@ -8682,10 +8682,10 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="B343" s="5" t="s">
         <v>664</v>
-      </c>
-      <c r="B343" s="5" t="s">
-        <v>665</v>
       </c>
       <c r="C343" s="5" t="s">
         <v>292</v>
@@ -8697,10 +8697,10 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B344" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C344" s="5" t="s">
         <v>292</v>
@@ -8712,10 +8712,10 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" s="5" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C345" s="5" t="s">
         <v>292</v>
@@ -8727,10 +8727,10 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C346" s="5" t="s">
         <v>292</v>
@@ -8758,10 +8758,10 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" s="5" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B348" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C348" s="5" t="s">
         <v>300</v>
@@ -8773,10 +8773,10 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="B349" s="5" t="s">
         <v>446</v>
-      </c>
-      <c r="B349" s="5" t="s">
-        <v>447</v>
       </c>
       <c r="C349" s="5" t="s">
         <v>300</v>
@@ -8819,10 +8819,10 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="B352" s="5" t="s">
         <v>494</v>
-      </c>
-      <c r="B352" s="5" t="s">
-        <v>495</v>
       </c>
       <c r="C352" s="5" t="s">
         <v>292</v>
@@ -8850,13 +8850,13 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="11" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B354" s="11" t="s">
         <v>62</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E354">
         <f t="shared" si="11"/>
@@ -9054,13 +9054,13 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="B367" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="B367" s="5" t="s">
-        <v>428</v>
-      </c>
       <c r="C367" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E367">
         <f t="shared" si="11"/>
@@ -9069,13 +9069,13 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="B368" s="11" t="s">
         <v>581</v>
       </c>
-      <c r="B368" s="11" t="s">
-        <v>582</v>
-      </c>
       <c r="C368" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E368" t="str">
         <f t="shared" si="11"/>
@@ -9099,10 +9099,10 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="B370" s="5" t="s">
         <v>754</v>
-      </c>
-      <c r="B370" s="5" t="s">
-        <v>755</v>
       </c>
       <c r="C370" s="5" t="s">
         <v>300</v>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="B371" s="5" t="s">
         <v>699</v>
-      </c>
-      <c r="B371" s="5" t="s">
-        <v>700</v>
       </c>
       <c r="C371" s="5" t="s">
         <v>300</v>
@@ -9145,10 +9145,10 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="B373" s="5" t="s">
         <v>677</v>
-      </c>
-      <c r="B373" s="5" t="s">
-        <v>678</v>
       </c>
       <c r="C373" s="5" t="s">
         <v>292</v>
@@ -9175,10 +9175,10 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="B375" s="5" t="s">
         <v>625</v>
-      </c>
-      <c r="B375" s="5" t="s">
-        <v>626</v>
       </c>
       <c r="C375" s="5" t="s">
         <v>292</v>
@@ -9221,10 +9221,10 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="B378" s="5" t="s">
         <v>536</v>
-      </c>
-      <c r="B378" s="5" t="s">
-        <v>537</v>
       </c>
       <c r="C378" s="5" t="s">
         <v>292</v>
@@ -9236,10 +9236,10 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="B379" s="5" t="s">
         <v>515</v>
-      </c>
-      <c r="B379" s="5" t="s">
-        <v>516</v>
       </c>
       <c r="C379" s="5" t="s">
         <v>156</v>
@@ -9251,10 +9251,10 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B380" s="5" t="s">
         <v>448</v>
-      </c>
-      <c r="B380" s="5" t="s">
-        <v>449</v>
       </c>
       <c r="C380" s="5" t="s">
         <v>300</v>
@@ -9266,10 +9266,10 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" s="5" t="s">
+        <v>719</v>
+      </c>
+      <c r="B381" s="5" t="s">
         <v>720</v>
-      </c>
-      <c r="B381" s="5" t="s">
-        <v>721</v>
       </c>
       <c r="C381" s="5" t="s">
         <v>292</v>
@@ -9281,10 +9281,10 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" s="5" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B382" s="5" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C382" s="5" t="s">
         <v>300</v>
@@ -9296,10 +9296,10 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="B383" s="5" t="s">
         <v>696</v>
-      </c>
-      <c r="B383" s="5" t="s">
-        <v>697</v>
       </c>
       <c r="C383" s="5" t="s">
         <v>300</v>
@@ -9327,10 +9327,10 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="5" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C385" s="5" t="s">
         <v>292</v>
@@ -9342,10 +9342,10 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="5" t="s">
+        <v>727</v>
+      </c>
+      <c r="B386" s="5" t="s">
         <v>728</v>
-      </c>
-      <c r="B386" s="5" t="s">
-        <v>729</v>
       </c>
       <c r="C386" s="5" t="s">
         <v>292</v>
@@ -9373,13 +9373,13 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="B388" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="B388" s="11" t="s">
-        <v>559</v>
-      </c>
       <c r="C388" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E388" t="str">
         <f t="shared" si="11"/>
@@ -9388,13 +9388,13 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="11" t="s">
+        <v>590</v>
+      </c>
+      <c r="B389" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="B389" s="11" t="s">
+      <c r="C389" s="5" t="s">
         <v>592</v>
-      </c>
-      <c r="C389" s="5" t="s">
-        <v>593</v>
       </c>
       <c r="E389" t="str">
         <f t="shared" si="11"/>
@@ -9403,10 +9403,10 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="B390" s="5" t="s">
         <v>651</v>
-      </c>
-      <c r="B390" s="5" t="s">
-        <v>652</v>
       </c>
       <c r="C390" s="5" t="s">
         <v>292</v>
@@ -9433,10 +9433,10 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="B392" s="5" t="s">
         <v>642</v>
-      </c>
-      <c r="B392" s="5" t="s">
-        <v>643</v>
       </c>
       <c r="C392" s="5" t="s">
         <v>292</v>
@@ -9448,10 +9448,10 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="B393" s="5" t="s">
         <v>604</v>
-      </c>
-      <c r="B393" s="5" t="s">
-        <v>605</v>
       </c>
       <c r="C393" s="5" t="s">
         <v>292</v>
@@ -9463,10 +9463,10 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" s="5" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B394" s="5" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C394" s="5" t="s">
         <v>292</v>
@@ -9494,13 +9494,13 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="B396" s="5" t="s">
         <v>762</v>
       </c>
-      <c r="B396" s="5" t="s">
-        <v>763</v>
-      </c>
       <c r="C396" s="5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E396" t="str">
         <f t="shared" si="11"/>
@@ -9527,10 +9527,10 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="5" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C398" s="5" t="s">
         <v>292</v>
@@ -9542,10 +9542,10 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="B399" t="s">
         <v>792</v>
-      </c>
-      <c r="B399" t="s">
-        <v>793</v>
       </c>
       <c r="C399" s="5" t="s">
         <v>300</v>
@@ -9557,10 +9557,10 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" s="5" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B400" s="5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C400" s="5" t="s">
         <v>292</v>
@@ -9618,13 +9618,13 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="B404" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="B404" s="11" t="s">
-        <v>549</v>
-      </c>
       <c r="C404" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E404" t="str">
         <f t="shared" si="12"/>
@@ -9648,10 +9648,10 @@
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="B406" s="5" t="s">
         <v>508</v>
-      </c>
-      <c r="B406" s="5" t="s">
-        <v>509</v>
       </c>
       <c r="C406" s="5" t="s">
         <v>292</v>
@@ -9714,7 +9714,7 @@
         <v>32</v>
       </c>
       <c r="B410" s="5" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C410" s="5" t="s">
         <v>290</v>
@@ -9726,7 +9726,7 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B411" s="5" t="s">
         <v>33</v>
@@ -9775,13 +9775,13 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="B414" s="5" t="s">
         <v>736</v>
       </c>
-      <c r="B414" s="5" t="s">
-        <v>737</v>
-      </c>
       <c r="C414" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E414" t="str">
         <f t="shared" si="12"/>
@@ -15665,7 +15665,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.25">
@@ -15673,7 +15673,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15" x14ac:dyDescent="0.25">
@@ -15683,22 +15683,22 @@
     </row>
     <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
@@ -15708,17 +15708,17 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">

--- a/Mng/Acronyms.xlsx
+++ b/Mng/Acronyms.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C912A69D-99BE-47FE-9E96-271DF7B7A24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DA40D1-B631-404E-BDE5-29FFB0A2531E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294947668" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="860">
   <si>
     <t>GW</t>
   </si>
@@ -2877,6 +2877,18 @@
   </si>
   <si>
     <t>l_</t>
+  </si>
+  <si>
+    <t>Su</t>
+  </si>
+  <si>
+    <t>Summer</t>
+  </si>
+  <si>
+    <t>Wi</t>
+  </si>
+  <si>
+    <t>Winter</t>
   </si>
 </sst>
 </file>
@@ -9893,9 +9905,14 @@
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B421" s="5"/>
+      <c r="A421" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="B421" s="5" t="s">
+        <v>857</v>
+      </c>
       <c r="C421" s="5" t="s">
-        <v>156</v>
+        <v>300</v>
       </c>
       <c r="E421" t="str">
         <f t="shared" si="12"/>
@@ -9903,9 +9920,14 @@
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B422" s="5"/>
+      <c r="A422" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="B422" s="5" t="s">
+        <v>859</v>
+      </c>
       <c r="C422" s="5" t="s">
-        <v>156</v>
+        <v>300</v>
       </c>
       <c r="E422" t="str">
         <f t="shared" si="12"/>
